--- a/EpiRank_原/ERA_result_d_0.95_daytime_0.5_loops_309.xlsx
+++ b/EpiRank_原/ERA_result_d_0.95_daytime_0.5_loops_309.xlsx
@@ -1179,10 +1179,10 @@
         <v>0.01205</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA5" s="3" t="n">
         <v>11</v>
@@ -1334,7 +1334,7 @@
         <v>0.006652</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z6" s="3" t="n">
         <v>0</v>
@@ -2708,10 +2708,10 @@
         <v>0.004698</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA15" s="3" t="n">
         <v>4</v>
@@ -3008,10 +3008,10 @@
         <v>0.008274999999999999</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA17" s="3" t="n">
         <v>4</v>
@@ -3158,10 +3158,10 @@
         <v>0.008586</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA18" s="3" t="n">
         <v>3</v>
@@ -3308,10 +3308,10 @@
         <v>0.011024</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA19" s="3" t="n">
         <v>8</v>
@@ -4268,10 +4268,10 @@
         <v>0.007023</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA26" s="3" t="n">
         <v>8</v>
@@ -4918,10 +4918,10 @@
         <v>0.004713</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA31" s="3" t="n">
         <v>7</v>
@@ -5038,10 +5038,10 @@
         <v>0.005408</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA32" s="3" t="n">
         <v>7</v>
@@ -5521,7 +5521,7 @@
         <v>0</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA36" s="3" t="n">
         <v>5</v>
@@ -6718,10 +6718,10 @@
         <v>0.007706</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA46" s="3" t="n">
         <v>2</v>
@@ -6958,10 +6958,10 @@
         <v>0.006948</v>
       </c>
       <c r="Y48" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z48" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA48" s="3" t="n">
         <v>3</v>
@@ -7201,7 +7201,7 @@
         <v>0</v>
       </c>
       <c r="Z50" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA50" s="3" t="n">
         <v>5</v>
@@ -7438,7 +7438,7 @@
         <v>0.005555</v>
       </c>
       <c r="Y52" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z52" s="3" t="n">
         <v>-0</v>
@@ -7678,10 +7678,10 @@
         <v>0.004587</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA54" s="3" t="n">
         <v>2</v>
@@ -8398,7 +8398,7 @@
         <v>0.004618</v>
       </c>
       <c r="Y60" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z60" s="3" t="n">
         <v>-0</v>
@@ -8878,7 +8878,7 @@
         <v>0.0015</v>
       </c>
       <c r="Y64" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z64" s="3" t="n">
         <v>-0</v>
@@ -9578,10 +9578,10 @@
         <v>0.006096</v>
       </c>
       <c r="Y70" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z70" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA70" s="3" t="n">
         <v>1</v>
@@ -10241,7 +10241,7 @@
         <v>-0</v>
       </c>
       <c r="Z76" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA76" s="3" t="n">
         <v>0</v>
@@ -10348,10 +10348,10 @@
         <v>0.002616</v>
       </c>
       <c r="Y77" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z77" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA77" s="3" t="n">
         <v>2</v>
@@ -10458,10 +10458,10 @@
         <v>0.002491</v>
       </c>
       <c r="Y78" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z78" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA78" s="3" t="n">
         <v>6</v>
@@ -10681,7 +10681,7 @@
         <v>0</v>
       </c>
       <c r="Z80" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA80" s="3" t="n">
         <v>4</v>
@@ -11338,7 +11338,7 @@
         <v>0.003041</v>
       </c>
       <c r="Y86" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z86" s="3" t="n">
         <v>-0</v>
@@ -11558,10 +11558,10 @@
         <v>0.002613</v>
       </c>
       <c r="Y88" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z88" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA88" s="3" t="n">
         <v>2</v>
@@ -11998,10 +11998,10 @@
         <v>0.003408</v>
       </c>
       <c r="Y92" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z92" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA92" s="3" t="n">
         <v>1</v>
@@ -12108,10 +12108,10 @@
         <v>0.003716</v>
       </c>
       <c r="Y93" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z93" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA93" s="3" t="n">
         <v>0</v>
@@ -12328,10 +12328,10 @@
         <v>0.002268</v>
       </c>
       <c r="Y95" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z95" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA95" s="3" t="n">
         <v>0</v>
@@ -12768,10 +12768,10 @@
         <v>0.003882</v>
       </c>
       <c r="Y99" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z99" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA99" s="3" t="n">
         <v>0</v>
@@ -12878,10 +12878,10 @@
         <v>0.003369</v>
       </c>
       <c r="Y100" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z100" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA100" s="3" t="n">
         <v>2</v>
@@ -13868,10 +13868,10 @@
         <v>0.002802</v>
       </c>
       <c r="Y109" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z109" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA109" s="3" t="n">
         <v>0</v>
@@ -14091,7 +14091,7 @@
         <v>0</v>
       </c>
       <c r="Z111" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA111" s="3" t="n">
         <v>2</v>
@@ -14858,10 +14858,10 @@
         <v>0.002496</v>
       </c>
       <c r="Y118" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z118" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA118" s="3" t="n">
         <v>1</v>
@@ -15521,7 +15521,7 @@
         <v>0</v>
       </c>
       <c r="Z124" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA124" s="3" t="n">
         <v>0</v>
@@ -15628,10 +15628,10 @@
         <v>0.002787</v>
       </c>
       <c r="Y125" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z125" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA125" s="3" t="n">
         <v>2</v>
@@ -15741,7 +15741,7 @@
         <v>0</v>
       </c>
       <c r="Z126" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA126" s="3" t="n">
         <v>0</v>
@@ -15848,10 +15848,10 @@
         <v>0.002579</v>
       </c>
       <c r="Y127" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z127" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA127" s="3" t="n">
         <v>0</v>
@@ -16068,10 +16068,10 @@
         <v>0.002014</v>
       </c>
       <c r="Y129" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z129" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA129" s="3" t="n">
         <v>3</v>
@@ -16288,10 +16288,10 @@
         <v>0.00191</v>
       </c>
       <c r="Y131" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z131" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA131" s="3" t="n">
         <v>1</v>
@@ -16508,10 +16508,10 @@
         <v>0.003344</v>
       </c>
       <c r="Y133" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z133" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA133" s="3" t="n">
         <v>3</v>
@@ -16728,10 +16728,10 @@
         <v>0.004587</v>
       </c>
       <c r="Y135" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z135" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA135" s="3" t="n">
         <v>0</v>
@@ -16838,10 +16838,10 @@
         <v>0.002116</v>
       </c>
       <c r="Y136" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z136" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA136" s="3" t="n">
         <v>0</v>
@@ -17058,10 +17058,10 @@
         <v>0.002491</v>
       </c>
       <c r="Y138" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z138" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA138" s="3" t="n">
         <v>2</v>
@@ -17388,7 +17388,7 @@
         <v>0.001759</v>
       </c>
       <c r="Y141" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z141" s="3" t="n">
         <v>-0</v>
@@ -17718,10 +17718,10 @@
         <v>0.005244</v>
       </c>
       <c r="Y144" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z144" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA144" s="3" t="n">
         <v>2</v>
@@ -18488,10 +18488,10 @@
         <v>0.002174</v>
       </c>
       <c r="Y151" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z151" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA151" s="3" t="n">
         <v>1</v>
@@ -18711,7 +18711,7 @@
         <v>0</v>
       </c>
       <c r="Z153" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA153" s="3" t="n">
         <v>0</v>
@@ -18818,10 +18818,10 @@
         <v>0.001295</v>
       </c>
       <c r="Y154" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z154" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA154" s="3" t="n">
         <v>0</v>
@@ -19258,10 +19258,10 @@
         <v>0.003403</v>
       </c>
       <c r="Y158" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z158" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA158" s="3" t="n">
         <v>0</v>
@@ -19478,10 +19478,10 @@
         <v>0.004473</v>
       </c>
       <c r="Y160" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z160" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA160" s="3" t="n">
         <v>1</v>
@@ -19808,10 +19808,10 @@
         <v>0.002964</v>
       </c>
       <c r="Y163" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z163" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA163" s="3" t="n">
         <v>3</v>
@@ -20028,10 +20028,10 @@
         <v>0.002813</v>
       </c>
       <c r="Y165" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z165" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA165" s="3" t="n">
         <v>1</v>
@@ -20141,7 +20141,7 @@
         <v>0</v>
       </c>
       <c r="Z166" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA166" s="3" t="n">
         <v>2</v>
@@ -20248,10 +20248,10 @@
         <v>0.002432</v>
       </c>
       <c r="Y167" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z167" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA167" s="3" t="n">
         <v>1</v>
@@ -20468,10 +20468,10 @@
         <v>0.001501</v>
       </c>
       <c r="Y169" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z169" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA169" s="3" t="n">
         <v>1</v>
@@ -20908,10 +20908,10 @@
         <v>0.003364</v>
       </c>
       <c r="Y173" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z173" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA173" s="3" t="n">
         <v>0</v>
@@ -21241,7 +21241,7 @@
         <v>0</v>
       </c>
       <c r="Z176" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA176" s="3" t="n">
         <v>1</v>
@@ -21461,7 +21461,7 @@
         <v>0</v>
       </c>
       <c r="Z178" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA178" s="3" t="n">
         <v>2</v>
@@ -21678,10 +21678,10 @@
         <v>0.001235</v>
       </c>
       <c r="Y180" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z180" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA180" s="3" t="n">
         <v>1</v>
@@ -21791,7 +21791,7 @@
         <v>0</v>
       </c>
       <c r="Z181" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA181" s="3" t="n">
         <v>0</v>
@@ -21898,10 +21898,10 @@
         <v>0.0011</v>
       </c>
       <c r="Y182" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z182" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA182" s="3" t="n">
         <v>0</v>
@@ -22121,7 +22121,7 @@
         <v>0</v>
       </c>
       <c r="Z184" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA184" s="3" t="n">
         <v>0</v>
@@ -22341,7 +22341,7 @@
         <v>-0</v>
       </c>
       <c r="Z186" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA186" s="3" t="n">
         <v>1</v>
@@ -22448,10 +22448,10 @@
         <v>0.002618</v>
       </c>
       <c r="Y187" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z187" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA187" s="3" t="n">
         <v>0</v>
@@ -22558,10 +22558,10 @@
         <v>0.001669</v>
       </c>
       <c r="Y188" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z188" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA188" s="3" t="n">
         <v>0</v>
@@ -22668,10 +22668,10 @@
         <v>0.0009700000000000001</v>
       </c>
       <c r="Y189" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z189" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA189" s="3" t="n">
         <v>3</v>
@@ -22888,10 +22888,10 @@
         <v>0.001708</v>
       </c>
       <c r="Y191" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z191" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA191" s="3" t="n">
         <v>0</v>
@@ -22998,7 +22998,7 @@
         <v>0.002238</v>
       </c>
       <c r="Y192" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z192" s="3" t="n">
         <v>0</v>
@@ -23551,7 +23551,7 @@
         <v>0</v>
       </c>
       <c r="Z197" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA197" s="3" t="n">
         <v>1</v>
@@ -23878,10 +23878,10 @@
         <v>0.001686</v>
       </c>
       <c r="Y200" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z200" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA200" s="3" t="n">
         <v>1</v>
@@ -23988,7 +23988,7 @@
         <v>0.001259</v>
       </c>
       <c r="Y201" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z201" s="3" t="n">
         <v>-0</v>
@@ -24318,7 +24318,7 @@
         <v>0.002004</v>
       </c>
       <c r="Y204" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z204" s="3" t="n">
         <v>0</v>
@@ -24538,7 +24538,7 @@
         <v>0.001782</v>
       </c>
       <c r="Y206" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z206" s="3" t="n">
         <v>-0</v>
@@ -24978,10 +24978,10 @@
         <v>0.001245</v>
       </c>
       <c r="Y210" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z210" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA210" s="3" t="n">
         <v>0</v>
@@ -25311,7 +25311,7 @@
         <v>0</v>
       </c>
       <c r="Z213" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA213" s="3" t="n">
         <v>6</v>
@@ -25528,10 +25528,10 @@
         <v>0.002059</v>
       </c>
       <c r="Y215" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z215" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA215" s="3" t="n">
         <v>0</v>
@@ -25638,10 +25638,10 @@
         <v>0.0008140000000000001</v>
       </c>
       <c r="Y216" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z216" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA216" s="3" t="n">
         <v>0</v>
@@ -25751,7 +25751,7 @@
         <v>0</v>
       </c>
       <c r="Z217" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA217" s="3" t="n">
         <v>0</v>
@@ -25861,7 +25861,7 @@
         <v>-0</v>
       </c>
       <c r="Z218" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA218" s="3" t="n">
         <v>0</v>
@@ -26078,10 +26078,10 @@
         <v>0.001943</v>
       </c>
       <c r="Y220" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z220" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA220" s="3" t="n">
         <v>0</v>
@@ -26391,7 +26391,7 @@
         <v>-0</v>
       </c>
       <c r="Z223" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA223" s="3" t="n">
         <v>6</v>
@@ -26588,10 +26588,10 @@
         <v>0.00135</v>
       </c>
       <c r="Y225" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z225" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA225" s="3" t="n">
         <v>0</v>
@@ -26788,10 +26788,10 @@
         <v>0.001152</v>
       </c>
       <c r="Y227" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z227" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA227" s="3" t="n">
         <v>0</v>
@@ -26988,7 +26988,7 @@
         <v>0.00125</v>
       </c>
       <c r="Y229" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z229" s="3" t="n">
         <v>0</v>
@@ -27091,7 +27091,7 @@
         <v>0</v>
       </c>
       <c r="Z230" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA230" s="3" t="n">
         <v>2</v>
@@ -27291,7 +27291,7 @@
         <v>0</v>
       </c>
       <c r="Z232" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA232" s="3" t="n">
         <v>0</v>
@@ -27488,7 +27488,7 @@
         <v>0.001</v>
       </c>
       <c r="Y234" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z234" s="3" t="n">
         <v>-0</v>
@@ -27588,10 +27588,10 @@
         <v>0.001309</v>
       </c>
       <c r="Y235" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z235" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA235" s="3" t="n">
         <v>0</v>
@@ -27688,7 +27688,7 @@
         <v>0.001592</v>
       </c>
       <c r="Y236" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z236" s="3" t="n">
         <v>-0</v>
@@ -27788,10 +27788,10 @@
         <v>0.00164</v>
       </c>
       <c r="Y237" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z237" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA237" s="3" t="n">
         <v>0</v>
@@ -27891,7 +27891,7 @@
         <v>0</v>
       </c>
       <c r="Z238" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA238" s="3" t="n">
         <v>2</v>
@@ -28188,7 +28188,7 @@
         <v>0.001513</v>
       </c>
       <c r="Y241" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z241" s="3" t="n">
         <v>0</v>
@@ -28391,7 +28391,7 @@
         <v>0</v>
       </c>
       <c r="Z243" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA243" s="3" t="n">
         <v>0</v>
@@ -28491,7 +28491,7 @@
         <v>0</v>
       </c>
       <c r="Z244" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA244" s="3" t="n">
         <v>3</v>
@@ -28591,7 +28591,7 @@
         <v>0</v>
       </c>
       <c r="Z245" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA245" s="3" t="n">
         <v>1</v>
@@ -28688,7 +28688,7 @@
         <v>0.002084</v>
       </c>
       <c r="Y246" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z246" s="3" t="n">
         <v>-0</v>
@@ -28791,7 +28791,7 @@
         <v>-0</v>
       </c>
       <c r="Z247" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA247" s="3" t="n">
         <v>0</v>
@@ -28988,10 +28988,10 @@
         <v>0.001148</v>
       </c>
       <c r="Y249" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z249" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA249" s="3" t="n">
         <v>0</v>
@@ -29088,10 +29088,10 @@
         <v>0.001877</v>
       </c>
       <c r="Y250" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z250" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA250" s="3" t="n">
         <v>0</v>
@@ -29391,7 +29391,7 @@
         <v>0</v>
       </c>
       <c r="Z253" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA253" s="3" t="n">
         <v>2</v>
@@ -29488,10 +29488,10 @@
         <v>0.001296</v>
       </c>
       <c r="Y254" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z254" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA254" s="3" t="n">
         <v>1</v>
@@ -29691,7 +29691,7 @@
         <v>-0</v>
       </c>
       <c r="Z256" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA256" s="3" t="n">
         <v>0</v>
@@ -29991,7 +29991,7 @@
         <v>-0</v>
       </c>
       <c r="Z259" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA259" s="3" t="n">
         <v>0</v>
@@ -30091,7 +30091,7 @@
         <v>0</v>
       </c>
       <c r="Z260" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA260" s="3" t="n">
         <v>0</v>
@@ -30188,7 +30188,7 @@
         <v>0.001556</v>
       </c>
       <c r="Y261" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z261" s="3" t="n">
         <v>-0</v>
@@ -30288,7 +30288,7 @@
         <v>0.000785</v>
       </c>
       <c r="Y262" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z262" s="3" t="n">
         <v>-0</v>
@@ -30588,7 +30588,7 @@
         <v>0.00079</v>
       </c>
       <c r="Y265" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z265" s="3" t="n">
         <v>-0</v>
@@ -30788,7 +30788,7 @@
         <v>0.001386</v>
       </c>
       <c r="Y267" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z267" s="3" t="n">
         <v>-0</v>
@@ -31391,7 +31391,7 @@
         <v>0</v>
       </c>
       <c r="Z273" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA273" s="3" t="n">
         <v>1</v>
@@ -31591,7 +31591,7 @@
         <v>0</v>
       </c>
       <c r="Z275" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA275" s="3" t="n">
         <v>1</v>
@@ -31888,7 +31888,7 @@
         <v>0.001032</v>
       </c>
       <c r="Y278" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z278" s="3" t="n">
         <v>-0</v>
@@ -31991,7 +31991,7 @@
         <v>-0</v>
       </c>
       <c r="Z279" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA279" s="3" t="n">
         <v>0</v>
@@ -32191,7 +32191,7 @@
         <v>0</v>
       </c>
       <c r="Z281" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA281" s="3" t="n">
         <v>0</v>
@@ -32288,10 +32288,10 @@
         <v>0.0009479999999999999</v>
       </c>
       <c r="Y282" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z282" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA282" s="3" t="n">
         <v>0</v>
@@ -32588,7 +32588,7 @@
         <v>0.00143</v>
       </c>
       <c r="Y285" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z285" s="3" t="n">
         <v>-0</v>
@@ -32891,7 +32891,7 @@
         <v>0</v>
       </c>
       <c r="Z288" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA288" s="3" t="n">
         <v>1</v>
@@ -33088,10 +33088,10 @@
         <v>0.00315</v>
       </c>
       <c r="Y290" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z290" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA290" s="3" t="n">
         <v>0</v>
@@ -33291,7 +33291,7 @@
         <v>-0</v>
       </c>
       <c r="Z292" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA292" s="3" t="n">
         <v>0</v>
@@ -33691,7 +33691,7 @@
         <v>0</v>
       </c>
       <c r="Z296" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA296" s="3" t="n">
         <v>0</v>
@@ -33788,7 +33788,7 @@
         <v>0.000837</v>
       </c>
       <c r="Y297" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z297" s="3" t="n">
         <v>-0</v>
@@ -34288,7 +34288,7 @@
         <v>0.00126</v>
       </c>
       <c r="Y302" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z302" s="3" t="n">
         <v>0</v>
@@ -34788,7 +34788,7 @@
         <v>0.000827</v>
       </c>
       <c r="Y307" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z307" s="3" t="n">
         <v>0</v>
@@ -35388,7 +35388,7 @@
         <v>0.001773</v>
       </c>
       <c r="Y313" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z313" s="3" t="n">
         <v>-0</v>
@@ -35491,7 +35491,7 @@
         <v>0</v>
       </c>
       <c r="Z314" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA314" s="3" t="n">
         <v>0</v>
@@ -35991,7 +35991,7 @@
         <v>0</v>
       </c>
       <c r="Z319" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA319" s="3" t="n">
         <v>3</v>
@@ -36088,10 +36088,10 @@
         <v>0.000803</v>
       </c>
       <c r="Y320" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z320" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA320" s="3" t="n">
         <v>1</v>
@@ -37988,10 +37988,10 @@
         <v>0.001203</v>
       </c>
       <c r="Y339" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z339" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA339" s="3" t="n">
         <v>0</v>
@@ -38588,10 +38588,10 @@
         <v>0.000592</v>
       </c>
       <c r="Y345" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z345" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA345" s="3" t="n">
         <v>0</v>
@@ -39388,7 +39388,7 @@
         <v>0.000518</v>
       </c>
       <c r="Y353" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z353" s="3" t="n">
         <v>0</v>
@@ -39556,10 +39556,10 @@
         <v>0.529801</v>
       </c>
       <c r="Y356" s="3" t="n">
-        <v>0.220335</v>
+        <v>0.11126</v>
       </c>
       <c r="Z356" s="3" t="n">
-        <v>0.171702</v>
+        <v>0.130604</v>
       </c>
       <c r="AB356" s="3" t="n">
         <v>0.599035</v>
@@ -39610,10 +39610,10 @@
         <v>0.445424</v>
       </c>
       <c r="Y358" s="3" t="n">
-        <v>0.45149</v>
+        <v>0.418443</v>
       </c>
       <c r="Z358" s="3" t="n">
-        <v>0.419798</v>
+        <v>0.390682</v>
       </c>
       <c r="AA358" s="3" t="n">
         <v>0.531073</v>
@@ -39985,10 +39985,10 @@
         <v>0.386474</v>
       </c>
       <c r="D8" t="n">
-        <v>0.45149</v>
+        <v>0.418443</v>
       </c>
       <c r="E8" t="n">
-        <v>0.34611</v>
+        <v>0.316891</v>
       </c>
       <c r="F8" t="n">
         <v>0.2988505747126437</v>
@@ -40015,10 +40015,10 @@
         <v>0.216528</v>
       </c>
       <c r="D9" t="n">
-        <v>0.220335</v>
+        <v>0.11126</v>
       </c>
       <c r="E9" t="n">
-        <v>0.164159</v>
+        <v>0.081349</v>
       </c>
       <c r="F9" t="n">
         <v>0.1641791044776119</v>
@@ -40045,10 +40045,10 @@
         <v>0.41859</v>
       </c>
       <c r="D10" t="n">
-        <v>0.367122</v>
+        <v>0.351733</v>
       </c>
       <c r="E10" t="n">
-        <v>0.29728</v>
+        <v>0.28563</v>
       </c>
       <c r="F10" t="n">
         <v>0.3636363636363636</v>
@@ -40075,10 +40075,10 @@
         <v>0.397421</v>
       </c>
       <c r="D11" t="n">
-        <v>0.419798</v>
+        <v>0.390682</v>
       </c>
       <c r="E11" t="n">
-        <v>0.316712</v>
+        <v>0.29207</v>
       </c>
       <c r="F11" t="n">
         <v>0.3333333333333333</v>
@@ -40105,10 +40105,10 @@
         <v>0.219019</v>
       </c>
       <c r="D12" t="n">
-        <v>0.171702</v>
+        <v>0.130604</v>
       </c>
       <c r="E12" t="n">
-        <v>0.123751</v>
+        <v>0.095369</v>
       </c>
       <c r="F12" t="n">
         <v>0.1716417910447761</v>
@@ -40135,10 +40135,10 @@
         <v>0.43754</v>
       </c>
       <c r="D13" t="n">
-        <v>0.344363</v>
+        <v>0.359874</v>
       </c>
       <c r="E13" t="n">
-        <v>0.27891</v>
+        <v>0.291959</v>
       </c>
       <c r="F13" t="n">
         <v>0.3939393939393939</v>

--- a/EpiRank_原/ERA_result_d_0.95_daytime_0.5_loops_309.xlsx
+++ b/EpiRank_原/ERA_result_d_0.95_daytime_0.5_loops_309.xlsx
@@ -714,10 +714,10 @@
         <v>0.012835</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA2" s="3" t="n">
         <v>9</v>
@@ -1334,7 +1334,7 @@
         <v>0.006652</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z6" s="3" t="n">
         <v>0</v>
@@ -1636,10 +1636,10 @@
         <v>0.016941</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA8" s="3" t="n">
         <v>8</v>
@@ -1787,10 +1787,10 @@
         <v>0.011997</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA9" s="3" t="n">
         <v>4</v>
@@ -2093,10 +2093,10 @@
         <v>0.009434</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA11" s="3" t="n">
         <v>2</v>
@@ -4268,10 +4268,10 @@
         <v>0.007023</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA26" s="3" t="n">
         <v>8</v>
@@ -6478,10 +6478,10 @@
         <v>0.004917</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA44" s="3" t="n">
         <v>2</v>
@@ -7438,10 +7438,10 @@
         <v>0.005555</v>
       </c>
       <c r="Y52" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z52" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA52" s="3" t="n">
         <v>2</v>
@@ -8401,7 +8401,7 @@
         <v>0</v>
       </c>
       <c r="Z60" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA60" s="3" t="n">
         <v>6</v>
@@ -8881,7 +8881,7 @@
         <v>0</v>
       </c>
       <c r="Z64" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA64" s="3" t="n">
         <v>35</v>
@@ -9578,10 +9578,10 @@
         <v>0.006096</v>
       </c>
       <c r="Y70" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z70" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA70" s="3" t="n">
         <v>1</v>
@@ -10018,10 +10018,10 @@
         <v>0.002648</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z74" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA74" s="3" t="n">
         <v>4</v>
@@ -10241,7 +10241,7 @@
         <v>-0</v>
       </c>
       <c r="Z76" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA76" s="3" t="n">
         <v>0</v>
@@ -10788,10 +10788,10 @@
         <v>0.004355</v>
       </c>
       <c r="Y81" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z81" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA81" s="3" t="n">
         <v>0</v>
@@ -11341,7 +11341,7 @@
         <v>0</v>
       </c>
       <c r="Z86" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA86" s="3" t="n">
         <v>1</v>
@@ -11561,7 +11561,7 @@
         <v>0</v>
       </c>
       <c r="Z88" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA88" s="3" t="n">
         <v>2</v>
@@ -11998,10 +11998,10 @@
         <v>0.003408</v>
       </c>
       <c r="Y92" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z92" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA92" s="3" t="n">
         <v>1</v>
@@ -12108,10 +12108,10 @@
         <v>0.003716</v>
       </c>
       <c r="Y93" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z93" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA93" s="3" t="n">
         <v>0</v>
@@ -12218,10 +12218,10 @@
         <v>0.002947</v>
       </c>
       <c r="Y94" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z94" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA94" s="3" t="n">
         <v>3</v>
@@ -12328,10 +12328,10 @@
         <v>0.002268</v>
       </c>
       <c r="Y95" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z95" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA95" s="3" t="n">
         <v>0</v>
@@ -12438,10 +12438,10 @@
         <v>0.003781</v>
       </c>
       <c r="Y96" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z96" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA96" s="3" t="n">
         <v>0</v>
@@ -13318,10 +13318,10 @@
         <v>0.003197</v>
       </c>
       <c r="Y104" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z104" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA104" s="3" t="n">
         <v>1</v>
@@ -13538,10 +13538,10 @@
         <v>0.002715</v>
       </c>
       <c r="Y106" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z106" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA106" s="3" t="n">
         <v>1</v>
@@ -14088,7 +14088,7 @@
         <v>0.001988</v>
       </c>
       <c r="Y111" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z111" s="3" t="n">
         <v>-0</v>
@@ -14308,10 +14308,10 @@
         <v>0.002806</v>
       </c>
       <c r="Y113" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z113" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA113" s="3" t="n">
         <v>0</v>
@@ -14748,10 +14748,10 @@
         <v>0.002833</v>
       </c>
       <c r="Y117" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z117" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA117" s="3" t="n">
         <v>1</v>
@@ -15521,7 +15521,7 @@
         <v>0</v>
       </c>
       <c r="Z124" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA124" s="3" t="n">
         <v>0</v>
@@ -15628,10 +15628,10 @@
         <v>0.002787</v>
       </c>
       <c r="Y125" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z125" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA125" s="3" t="n">
         <v>2</v>
@@ -15741,7 +15741,7 @@
         <v>0</v>
       </c>
       <c r="Z126" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA126" s="3" t="n">
         <v>0</v>
@@ -16068,10 +16068,10 @@
         <v>0.002014</v>
       </c>
       <c r="Y129" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z129" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA129" s="3" t="n">
         <v>3</v>
@@ -16178,10 +16178,10 @@
         <v>0.002381</v>
       </c>
       <c r="Y130" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z130" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA130" s="3" t="n">
         <v>2</v>
@@ -16398,10 +16398,10 @@
         <v>0.002147</v>
       </c>
       <c r="Y132" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z132" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA132" s="3" t="n">
         <v>1</v>
@@ -16838,10 +16838,10 @@
         <v>0.002116</v>
       </c>
       <c r="Y136" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z136" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA136" s="3" t="n">
         <v>0</v>
@@ -17061,7 +17061,7 @@
         <v>0</v>
       </c>
       <c r="Z138" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA138" s="3" t="n">
         <v>2</v>
@@ -17168,10 +17168,10 @@
         <v>0.002578</v>
       </c>
       <c r="Y139" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z139" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA139" s="3" t="n">
         <v>0</v>
@@ -17391,7 +17391,7 @@
         <v>0</v>
       </c>
       <c r="Z141" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA141" s="3" t="n">
         <v>1</v>
@@ -17498,10 +17498,10 @@
         <v>0.002604</v>
       </c>
       <c r="Y142" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z142" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA142" s="3" t="n">
         <v>7</v>
@@ -17938,10 +17938,10 @@
         <v>0.00181</v>
       </c>
       <c r="Y146" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z146" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA146" s="3" t="n">
         <v>1</v>
@@ -18488,7 +18488,7 @@
         <v>0.002174</v>
       </c>
       <c r="Y151" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z151" s="3" t="n">
         <v>0</v>
@@ -18708,10 +18708,10 @@
         <v>0.001664</v>
       </c>
       <c r="Y153" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z153" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA153" s="3" t="n">
         <v>0</v>
@@ -18818,10 +18818,10 @@
         <v>0.001295</v>
       </c>
       <c r="Y154" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z154" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA154" s="3" t="n">
         <v>0</v>
@@ -19258,10 +19258,10 @@
         <v>0.003403</v>
       </c>
       <c r="Y158" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z158" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA158" s="3" t="n">
         <v>0</v>
@@ -19481,7 +19481,7 @@
         <v>-0</v>
       </c>
       <c r="Z160" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA160" s="3" t="n">
         <v>1</v>
@@ -20248,10 +20248,10 @@
         <v>0.002432</v>
       </c>
       <c r="Y167" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z167" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA167" s="3" t="n">
         <v>1</v>
@@ -20908,10 +20908,10 @@
         <v>0.003364</v>
       </c>
       <c r="Y173" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z173" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA173" s="3" t="n">
         <v>0</v>
@@ -21018,10 +21018,10 @@
         <v>0.002818</v>
       </c>
       <c r="Y174" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z174" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA174" s="3" t="n">
         <v>0</v>
@@ -21128,7 +21128,7 @@
         <v>0.001797</v>
       </c>
       <c r="Y175" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z175" s="3" t="n">
         <v>0</v>
@@ -21461,7 +21461,7 @@
         <v>0</v>
       </c>
       <c r="Z178" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA178" s="3" t="n">
         <v>2</v>
@@ -21678,10 +21678,10 @@
         <v>0.001235</v>
       </c>
       <c r="Y180" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z180" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA180" s="3" t="n">
         <v>1</v>
@@ -21788,7 +21788,7 @@
         <v>0.002087</v>
       </c>
       <c r="Y181" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z181" s="3" t="n">
         <v>-0</v>
@@ -22118,7 +22118,7 @@
         <v>0.002161</v>
       </c>
       <c r="Y184" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z184" s="3" t="n">
         <v>-0</v>
@@ -22341,7 +22341,7 @@
         <v>-0</v>
       </c>
       <c r="Z186" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA186" s="3" t="n">
         <v>1</v>
@@ -22448,10 +22448,10 @@
         <v>0.002618</v>
       </c>
       <c r="Y187" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z187" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA187" s="3" t="n">
         <v>0</v>
@@ -22558,10 +22558,10 @@
         <v>0.001669</v>
       </c>
       <c r="Y188" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z188" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA188" s="3" t="n">
         <v>0</v>
@@ -22778,7 +22778,7 @@
         <v>0.00302</v>
       </c>
       <c r="Y190" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z190" s="3" t="n">
         <v>0</v>
@@ -23001,7 +23001,7 @@
         <v>-0</v>
       </c>
       <c r="Z192" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA192" s="3" t="n">
         <v>0</v>
@@ -23328,10 +23328,10 @@
         <v>0.001901</v>
       </c>
       <c r="Y195" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z195" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA195" s="3" t="n">
         <v>0</v>
@@ -23661,7 +23661,7 @@
         <v>-0</v>
       </c>
       <c r="Z198" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA198" s="3" t="n">
         <v>0</v>
@@ -23988,7 +23988,7 @@
         <v>0.001259</v>
       </c>
       <c r="Y201" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z201" s="3" t="n">
         <v>-0</v>
@@ -24318,7 +24318,7 @@
         <v>0.002004</v>
       </c>
       <c r="Y204" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z204" s="3" t="n">
         <v>0</v>
@@ -24538,7 +24538,7 @@
         <v>0.001782</v>
       </c>
       <c r="Y206" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z206" s="3" t="n">
         <v>-0</v>
@@ -24761,7 +24761,7 @@
         <v>0</v>
       </c>
       <c r="Z208" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA208" s="3" t="n">
         <v>1</v>
@@ -24978,10 +24978,10 @@
         <v>0.001245</v>
       </c>
       <c r="Y210" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z210" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA210" s="3" t="n">
         <v>0</v>
@@ -25088,7 +25088,7 @@
         <v>0.001081</v>
       </c>
       <c r="Y211" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z211" s="3" t="n">
         <v>-0</v>
@@ -25638,10 +25638,10 @@
         <v>0.0008140000000000001</v>
       </c>
       <c r="Y216" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z216" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA216" s="3" t="n">
         <v>0</v>
@@ -25748,10 +25748,10 @@
         <v>0.000905</v>
       </c>
       <c r="Y217" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z217" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA217" s="3" t="n">
         <v>0</v>
@@ -26078,7 +26078,7 @@
         <v>0.001943</v>
       </c>
       <c r="Y220" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z220" s="3" t="n">
         <v>-0</v>
@@ -26391,7 +26391,7 @@
         <v>-0</v>
       </c>
       <c r="Z223" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA223" s="3" t="n">
         <v>6</v>
@@ -26588,10 +26588,10 @@
         <v>0.00135</v>
       </c>
       <c r="Y225" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z225" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA225" s="3" t="n">
         <v>0</v>
@@ -26788,7 +26788,7 @@
         <v>0.001152</v>
       </c>
       <c r="Y227" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z227" s="3" t="n">
         <v>-0</v>
@@ -26988,10 +26988,10 @@
         <v>0.00125</v>
       </c>
       <c r="Y229" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z229" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA229" s="3" t="n">
         <v>0</v>
@@ -27291,7 +27291,7 @@
         <v>0</v>
       </c>
       <c r="Z232" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA232" s="3" t="n">
         <v>0</v>
@@ -27588,10 +27588,10 @@
         <v>0.001309</v>
       </c>
       <c r="Y235" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z235" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA235" s="3" t="n">
         <v>0</v>
@@ -27688,7 +27688,7 @@
         <v>0.001592</v>
       </c>
       <c r="Y236" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z236" s="3" t="n">
         <v>-0</v>
@@ -28388,10 +28388,10 @@
         <v>0.001248</v>
       </c>
       <c r="Y243" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z243" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA243" s="3" t="n">
         <v>0</v>
@@ -28591,7 +28591,7 @@
         <v>0</v>
       </c>
       <c r="Z245" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA245" s="3" t="n">
         <v>1</v>
@@ -28688,10 +28688,10 @@
         <v>0.002084</v>
       </c>
       <c r="Y246" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z246" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA246" s="3" t="n">
         <v>2</v>
@@ -28788,10 +28788,10 @@
         <v>0.001352</v>
       </c>
       <c r="Y247" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z247" s="3" t="n">
         <v>-0</v>
-      </c>
-      <c r="Z247" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="AA247" s="3" t="n">
         <v>0</v>
@@ -28891,7 +28891,7 @@
         <v>0</v>
       </c>
       <c r="Z248" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA248" s="3" t="n">
         <v>0</v>
@@ -28988,10 +28988,10 @@
         <v>0.001148</v>
       </c>
       <c r="Y249" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z249" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA249" s="3" t="n">
         <v>0</v>
@@ -29088,10 +29088,10 @@
         <v>0.001877</v>
       </c>
       <c r="Y250" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z250" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA250" s="3" t="n">
         <v>0</v>
@@ -29388,7 +29388,7 @@
         <v>0.001506</v>
       </c>
       <c r="Y253" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z253" s="3" t="n">
         <v>-0</v>
@@ -29488,7 +29488,7 @@
         <v>0.001296</v>
       </c>
       <c r="Y254" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z254" s="3" t="n">
         <v>0</v>
@@ -29691,7 +29691,7 @@
         <v>-0</v>
       </c>
       <c r="Z256" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA256" s="3" t="n">
         <v>0</v>
@@ -29891,7 +29891,7 @@
         <v>0</v>
       </c>
       <c r="Z258" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA258" s="3" t="n">
         <v>2</v>
@@ -30088,10 +30088,10 @@
         <v>0.000867</v>
       </c>
       <c r="Y260" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z260" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA260" s="3" t="n">
         <v>0</v>
@@ -30288,10 +30288,10 @@
         <v>0.000785</v>
       </c>
       <c r="Y262" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z262" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA262" s="3" t="n">
         <v>0</v>
@@ -30788,10 +30788,10 @@
         <v>0.001386</v>
       </c>
       <c r="Y267" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z267" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA267" s="3" t="n">
         <v>0</v>
@@ -32191,7 +32191,7 @@
         <v>0</v>
       </c>
       <c r="Z281" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA281" s="3" t="n">
         <v>0</v>
@@ -32291,7 +32291,7 @@
         <v>-0</v>
       </c>
       <c r="Z282" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA282" s="3" t="n">
         <v>0</v>
@@ -32591,7 +32591,7 @@
         <v>-0</v>
       </c>
       <c r="Z285" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA285" s="3" t="n">
         <v>0</v>
@@ -32688,10 +32688,10 @@
         <v>0.00209</v>
       </c>
       <c r="Y286" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z286" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA286" s="3" t="n">
         <v>1</v>
@@ -33288,10 +33288,10 @@
         <v>0.001184</v>
       </c>
       <c r="Y292" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z292" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA292" s="3" t="n">
         <v>0</v>
@@ -33588,10 +33588,10 @@
         <v>0.001378</v>
       </c>
       <c r="Y295" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z295" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA295" s="3" t="n">
         <v>2</v>
@@ -34091,7 +34091,7 @@
         <v>0</v>
       </c>
       <c r="Z300" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA300" s="3" t="n">
         <v>9</v>
@@ -34291,7 +34291,7 @@
         <v>-0</v>
       </c>
       <c r="Z302" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA302" s="3" t="n">
         <v>0</v>
@@ -34491,7 +34491,7 @@
         <v>0</v>
       </c>
       <c r="Z304" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA304" s="3" t="n">
         <v>0</v>
@@ -34688,10 +34688,10 @@
         <v>0.001202</v>
       </c>
       <c r="Y306" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z306" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA306" s="3" t="n">
         <v>0</v>
@@ -34791,7 +34791,7 @@
         <v>-0</v>
       </c>
       <c r="Z307" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA307" s="3" t="n">
         <v>0</v>
@@ -34888,10 +34888,10 @@
         <v>0.001097</v>
       </c>
       <c r="Y308" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z308" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA308" s="3" t="n">
         <v>0</v>
@@ -34988,10 +34988,10 @@
         <v>0.000803</v>
       </c>
       <c r="Y309" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z309" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA309" s="3" t="n">
         <v>0</v>
@@ -35188,7 +35188,7 @@
         <v>0.001123</v>
       </c>
       <c r="Y311" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z311" s="3" t="n">
         <v>0</v>
@@ -35391,7 +35391,7 @@
         <v>-0</v>
       </c>
       <c r="Z313" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA313" s="3" t="n">
         <v>1</v>
@@ -35791,7 +35791,7 @@
         <v>0</v>
       </c>
       <c r="Z317" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA317" s="3" t="n">
         <v>0</v>
@@ -36091,7 +36091,7 @@
         <v>-0</v>
       </c>
       <c r="Z320" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA320" s="3" t="n">
         <v>1</v>
@@ -36488,10 +36488,10 @@
         <v>0.00087</v>
       </c>
       <c r="Y324" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z324" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA324" s="3" t="n">
         <v>0</v>
@@ -37888,10 +37888,10 @@
         <v>0.00122</v>
       </c>
       <c r="Y338" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z338" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA338" s="3" t="n">
         <v>0</v>
@@ -37991,7 +37991,7 @@
         <v>-0</v>
       </c>
       <c r="Z339" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA339" s="3" t="n">
         <v>0</v>
@@ -38488,7 +38488,7 @@
         <v>0.000561</v>
       </c>
       <c r="Y344" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z344" s="3" t="n">
         <v>0</v>
@@ -38591,7 +38591,7 @@
         <v>-0</v>
       </c>
       <c r="Z345" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA345" s="3" t="n">
         <v>0</v>
@@ -39391,7 +39391,7 @@
         <v>-0</v>
       </c>
       <c r="Z353" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA353" s="3" t="n">
         <v>0</v>
@@ -39556,10 +39556,10 @@
         <v>0.529801</v>
       </c>
       <c r="Y356" s="3" t="n">
-        <v>0.11126</v>
+        <v>0.047472</v>
       </c>
       <c r="Z356" s="3" t="n">
-        <v>0.130604</v>
+        <v>0.078362</v>
       </c>
       <c r="AB356" s="3" t="n">
         <v>0.599035</v>
@@ -39610,10 +39610,10 @@
         <v>0.445424</v>
       </c>
       <c r="Y358" s="3" t="n">
-        <v>0.418443</v>
+        <v>0.380211</v>
       </c>
       <c r="Z358" s="3" t="n">
-        <v>0.390682</v>
+        <v>0.358513</v>
       </c>
       <c r="AA358" s="3" t="n">
         <v>0.531073</v>
@@ -39985,10 +39985,10 @@
         <v>0.386474</v>
       </c>
       <c r="D8" t="n">
-        <v>0.418443</v>
+        <v>0.380211</v>
       </c>
       <c r="E8" t="n">
-        <v>0.316891</v>
+        <v>0.28599</v>
       </c>
       <c r="F8" t="n">
         <v>0.2988505747126437</v>
@@ -40015,10 +40015,10 @@
         <v>0.216528</v>
       </c>
       <c r="D9" t="n">
-        <v>0.11126</v>
+        <v>0.047472</v>
       </c>
       <c r="E9" t="n">
-        <v>0.081349</v>
+        <v>0.034619</v>
       </c>
       <c r="F9" t="n">
         <v>0.1641791044776119</v>
@@ -40045,10 +40045,10 @@
         <v>0.41859</v>
       </c>
       <c r="D10" t="n">
-        <v>0.351733</v>
+        <v>0.323194</v>
       </c>
       <c r="E10" t="n">
-        <v>0.28563</v>
+        <v>0.261212</v>
       </c>
       <c r="F10" t="n">
         <v>0.3636363636363636</v>
@@ -40075,10 +40075,10 @@
         <v>0.397421</v>
       </c>
       <c r="D11" t="n">
-        <v>0.390682</v>
+        <v>0.358513</v>
       </c>
       <c r="E11" t="n">
-        <v>0.29207</v>
+        <v>0.265283</v>
       </c>
       <c r="F11" t="n">
         <v>0.3333333333333333</v>
@@ -40105,10 +40105,10 @@
         <v>0.219019</v>
       </c>
       <c r="D12" t="n">
-        <v>0.130604</v>
+        <v>0.078362</v>
       </c>
       <c r="E12" t="n">
-        <v>0.095369</v>
+        <v>0.05898</v>
       </c>
       <c r="F12" t="n">
         <v>0.1716417910447761</v>
@@ -40135,10 +40135,10 @@
         <v>0.43754</v>
       </c>
       <c r="D13" t="n">
-        <v>0.359874</v>
+        <v>0.310017</v>
       </c>
       <c r="E13" t="n">
-        <v>0.291959</v>
+        <v>0.249899</v>
       </c>
       <c r="F13" t="n">
         <v>0.3939393939393939</v>

--- a/EpiRank_原/ERA_result_d_0.95_daytime_0.5_loops_309.xlsx
+++ b/EpiRank_原/ERA_result_d_0.95_daytime_0.5_loops_309.xlsx
@@ -714,10 +714,10 @@
         <v>0.012835</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA2" s="3" t="n">
         <v>9</v>
@@ -1179,10 +1179,10 @@
         <v>0.01205</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA5" s="3" t="n">
         <v>11</v>
@@ -1787,10 +1787,10 @@
         <v>0.011997</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA9" s="3" t="n">
         <v>4</v>
@@ -2093,10 +2093,10 @@
         <v>0.009434</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA11" s="3" t="n">
         <v>2</v>
@@ -2708,10 +2708,10 @@
         <v>0.004698</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA15" s="3" t="n">
         <v>4</v>
@@ -3008,10 +3008,10 @@
         <v>0.008274999999999999</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA17" s="3" t="n">
         <v>4</v>
@@ -3158,10 +3158,10 @@
         <v>0.008586</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA18" s="3" t="n">
         <v>3</v>
@@ -4528,10 +4528,10 @@
         <v>0.01038</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA28" s="3" t="n">
         <v>0</v>
@@ -4658,10 +4658,10 @@
         <v>0.009729</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA29" s="3" t="n">
         <v>24</v>
@@ -5038,10 +5038,10 @@
         <v>0.005408</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA32" s="3" t="n">
         <v>7</v>
@@ -5518,10 +5518,10 @@
         <v>0.008265</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA36" s="3" t="n">
         <v>5</v>
@@ -6478,10 +6478,10 @@
         <v>0.004917</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA44" s="3" t="n">
         <v>2</v>
@@ -7438,10 +7438,10 @@
         <v>0.005555</v>
       </c>
       <c r="Y52" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z52" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA52" s="3" t="n">
         <v>2</v>
@@ -8878,10 +8878,10 @@
         <v>0.0015</v>
       </c>
       <c r="Y64" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z64" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA64" s="3" t="n">
         <v>35</v>
@@ -10348,7 +10348,7 @@
         <v>0.002616</v>
       </c>
       <c r="Y77" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z77" s="3" t="n">
         <v>-0</v>
@@ -11338,10 +11338,10 @@
         <v>0.003041</v>
       </c>
       <c r="Y86" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z86" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA86" s="3" t="n">
         <v>1</v>
@@ -12218,10 +12218,10 @@
         <v>0.002947</v>
       </c>
       <c r="Y94" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z94" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA94" s="3" t="n">
         <v>3</v>
@@ -12328,10 +12328,10 @@
         <v>0.002268</v>
       </c>
       <c r="Y95" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z95" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA95" s="3" t="n">
         <v>0</v>
@@ -12658,10 +12658,10 @@
         <v>0.0059</v>
       </c>
       <c r="Y98" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z98" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA98" s="3" t="n">
         <v>0</v>
@@ -12878,10 +12878,10 @@
         <v>0.003369</v>
       </c>
       <c r="Y100" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z100" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA100" s="3" t="n">
         <v>2</v>
@@ -14308,10 +14308,10 @@
         <v>0.002806</v>
       </c>
       <c r="Y113" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z113" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA113" s="3" t="n">
         <v>0</v>
@@ -14748,10 +14748,10 @@
         <v>0.002833</v>
       </c>
       <c r="Y117" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z117" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA117" s="3" t="n">
         <v>1</v>
@@ -14858,10 +14858,10 @@
         <v>0.002496</v>
       </c>
       <c r="Y118" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z118" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA118" s="3" t="n">
         <v>1</v>
@@ -15408,10 +15408,10 @@
         <v>0.002594</v>
       </c>
       <c r="Y123" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z123" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA123" s="3" t="n">
         <v>0</v>
@@ -15521,7 +15521,7 @@
         <v>0</v>
       </c>
       <c r="Z124" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA124" s="3" t="n">
         <v>0</v>
@@ -15628,10 +15628,10 @@
         <v>0.002787</v>
       </c>
       <c r="Y125" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z125" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA125" s="3" t="n">
         <v>2</v>
@@ -15741,7 +15741,7 @@
         <v>0</v>
       </c>
       <c r="Z126" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA126" s="3" t="n">
         <v>0</v>
@@ -15961,7 +15961,7 @@
         <v>0</v>
       </c>
       <c r="Z128" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA128" s="3" t="n">
         <v>1</v>
@@ -16068,10 +16068,10 @@
         <v>0.002014</v>
       </c>
       <c r="Y129" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z129" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA129" s="3" t="n">
         <v>3</v>
@@ -16398,10 +16398,10 @@
         <v>0.002147</v>
       </c>
       <c r="Y132" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z132" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA132" s="3" t="n">
         <v>1</v>
@@ -16508,10 +16508,10 @@
         <v>0.003344</v>
       </c>
       <c r="Y133" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z133" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA133" s="3" t="n">
         <v>3</v>
@@ -16728,10 +16728,10 @@
         <v>0.004587</v>
       </c>
       <c r="Y135" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z135" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA135" s="3" t="n">
         <v>0</v>
@@ -17061,7 +17061,7 @@
         <v>0</v>
       </c>
       <c r="Z138" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA138" s="3" t="n">
         <v>2</v>
@@ -17498,7 +17498,7 @@
         <v>0.002604</v>
       </c>
       <c r="Y142" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z142" s="3" t="n">
         <v>0</v>
@@ -17718,10 +17718,10 @@
         <v>0.005244</v>
       </c>
       <c r="Y144" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z144" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA144" s="3" t="n">
         <v>2</v>
@@ -17828,10 +17828,10 @@
         <v>0.001714</v>
       </c>
       <c r="Y145" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z145" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA145" s="3" t="n">
         <v>2</v>
@@ -17938,10 +17938,10 @@
         <v>0.00181</v>
       </c>
       <c r="Y146" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z146" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA146" s="3" t="n">
         <v>1</v>
@@ -18491,7 +18491,7 @@
         <v>-0</v>
       </c>
       <c r="Z151" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA151" s="3" t="n">
         <v>1</v>
@@ -18708,10 +18708,10 @@
         <v>0.001664</v>
       </c>
       <c r="Y153" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z153" s="3" t="n">
         <v>-0</v>
-      </c>
-      <c r="Z153" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="AA153" s="3" t="n">
         <v>0</v>
@@ -18818,10 +18818,10 @@
         <v>0.001295</v>
       </c>
       <c r="Y154" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z154" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA154" s="3" t="n">
         <v>0</v>
@@ -19258,10 +19258,10 @@
         <v>0.003403</v>
       </c>
       <c r="Y158" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z158" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA158" s="3" t="n">
         <v>0</v>
@@ -19368,10 +19368,10 @@
         <v>0.002542</v>
       </c>
       <c r="Y159" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z159" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA159" s="3" t="n">
         <v>1</v>
@@ -19478,7 +19478,7 @@
         <v>0.004473</v>
       </c>
       <c r="Y160" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z160" s="3" t="n">
         <v>0</v>
@@ -19808,10 +19808,10 @@
         <v>0.002964</v>
       </c>
       <c r="Y163" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z163" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA163" s="3" t="n">
         <v>3</v>
@@ -20028,10 +20028,10 @@
         <v>0.002813</v>
       </c>
       <c r="Y165" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z165" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA165" s="3" t="n">
         <v>1</v>
@@ -20138,7 +20138,7 @@
         <v>0.001963</v>
       </c>
       <c r="Y166" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z166" s="3" t="n">
         <v>-0</v>
@@ -20251,7 +20251,7 @@
         <v>-0</v>
       </c>
       <c r="Z167" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA167" s="3" t="n">
         <v>1</v>
@@ -21018,7 +21018,7 @@
         <v>0.002818</v>
       </c>
       <c r="Y174" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z174" s="3" t="n">
         <v>-0</v>
@@ -21131,7 +21131,7 @@
         <v>-0</v>
       </c>
       <c r="Z175" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA175" s="3" t="n">
         <v>0</v>
@@ -21241,7 +21241,7 @@
         <v>0</v>
       </c>
       <c r="Z176" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA176" s="3" t="n">
         <v>1</v>
@@ -21458,10 +21458,10 @@
         <v>0.001262</v>
       </c>
       <c r="Y178" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z178" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA178" s="3" t="n">
         <v>2</v>
@@ -21788,7 +21788,7 @@
         <v>0.002087</v>
       </c>
       <c r="Y181" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z181" s="3" t="n">
         <v>-0</v>
@@ -21901,7 +21901,7 @@
         <v>0</v>
       </c>
       <c r="Z182" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA182" s="3" t="n">
         <v>0</v>
@@ -22118,10 +22118,10 @@
         <v>0.002161</v>
       </c>
       <c r="Y184" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z184" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA184" s="3" t="n">
         <v>0</v>
@@ -22341,7 +22341,7 @@
         <v>-0</v>
       </c>
       <c r="Z186" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA186" s="3" t="n">
         <v>1</v>
@@ -22668,7 +22668,7 @@
         <v>0.0009700000000000001</v>
       </c>
       <c r="Y189" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z189" s="3" t="n">
         <v>-0</v>
@@ -22778,7 +22778,7 @@
         <v>0.00302</v>
       </c>
       <c r="Y190" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z190" s="3" t="n">
         <v>0</v>
@@ -22888,7 +22888,7 @@
         <v>0.001708</v>
       </c>
       <c r="Y191" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z191" s="3" t="n">
         <v>-0</v>
@@ -22998,10 +22998,10 @@
         <v>0.002238</v>
       </c>
       <c r="Y192" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z192" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA192" s="3" t="n">
         <v>0</v>
@@ -23328,10 +23328,10 @@
         <v>0.001901</v>
       </c>
       <c r="Y195" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z195" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA195" s="3" t="n">
         <v>0</v>
@@ -23438,10 +23438,10 @@
         <v>0.001326</v>
       </c>
       <c r="Y196" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z196" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA196" s="3" t="n">
         <v>0</v>
@@ -23658,7 +23658,7 @@
         <v>0.001192</v>
       </c>
       <c r="Y198" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z198" s="3" t="n">
         <v>0</v>
@@ -23768,7 +23768,7 @@
         <v>0.00185</v>
       </c>
       <c r="Y199" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z199" s="3" t="n">
         <v>0</v>
@@ -23878,10 +23878,10 @@
         <v>0.001686</v>
       </c>
       <c r="Y200" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z200" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA200" s="3" t="n">
         <v>1</v>
@@ -23988,10 +23988,10 @@
         <v>0.001259</v>
       </c>
       <c r="Y201" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z201" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA201" s="3" t="n">
         <v>1</v>
@@ -24761,7 +24761,7 @@
         <v>0</v>
       </c>
       <c r="Z208" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA208" s="3" t="n">
         <v>1</v>
@@ -24978,10 +24978,10 @@
         <v>0.001245</v>
       </c>
       <c r="Y210" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z210" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA210" s="3" t="n">
         <v>0</v>
@@ -25091,7 +25091,7 @@
         <v>0</v>
       </c>
       <c r="Z211" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA211" s="3" t="n">
         <v>3</v>
@@ -25308,7 +25308,7 @@
         <v>0.001495</v>
       </c>
       <c r="Y213" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z213" s="3" t="n">
         <v>-0</v>
@@ -25528,10 +25528,10 @@
         <v>0.002059</v>
       </c>
       <c r="Y215" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z215" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA215" s="3" t="n">
         <v>0</v>
@@ -25748,7 +25748,7 @@
         <v>0.000905</v>
       </c>
       <c r="Y217" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z217" s="3" t="n">
         <v>-0</v>
@@ -25858,10 +25858,10 @@
         <v>0.001577</v>
       </c>
       <c r="Y218" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z218" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA218" s="3" t="n">
         <v>0</v>
@@ -26078,7 +26078,7 @@
         <v>0.001943</v>
       </c>
       <c r="Y220" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z220" s="3" t="n">
         <v>-0</v>
@@ -26388,10 +26388,10 @@
         <v>0.001119</v>
       </c>
       <c r="Y223" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z223" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA223" s="3" t="n">
         <v>6</v>
@@ -26588,10 +26588,10 @@
         <v>0.00135</v>
       </c>
       <c r="Y225" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z225" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA225" s="3" t="n">
         <v>0</v>
@@ -26688,7 +26688,7 @@
         <v>0.001255</v>
       </c>
       <c r="Y226" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z226" s="3" t="n">
         <v>0</v>
@@ -26988,10 +26988,10 @@
         <v>0.00125</v>
       </c>
       <c r="Y229" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z229" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA229" s="3" t="n">
         <v>0</v>
@@ -27188,10 +27188,10 @@
         <v>0.001509</v>
       </c>
       <c r="Y231" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z231" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA231" s="3" t="n">
         <v>0</v>
@@ -27291,7 +27291,7 @@
         <v>0</v>
       </c>
       <c r="Z232" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA232" s="3" t="n">
         <v>0</v>
@@ -27488,10 +27488,10 @@
         <v>0.001</v>
       </c>
       <c r="Y234" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z234" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA234" s="3" t="n">
         <v>1</v>
@@ -27588,10 +27588,10 @@
         <v>0.001309</v>
       </c>
       <c r="Y235" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z235" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA235" s="3" t="n">
         <v>0</v>
@@ -27788,10 +27788,10 @@
         <v>0.00164</v>
       </c>
       <c r="Y237" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z237" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA237" s="3" t="n">
         <v>0</v>
@@ -27991,7 +27991,7 @@
         <v>0</v>
       </c>
       <c r="Z239" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA239" s="3" t="n">
         <v>2</v>
@@ -28388,7 +28388,7 @@
         <v>0.001248</v>
       </c>
       <c r="Y243" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z243" s="3" t="n">
         <v>-0</v>
@@ -28591,7 +28591,7 @@
         <v>0</v>
       </c>
       <c r="Z245" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA245" s="3" t="n">
         <v>1</v>
@@ -28688,10 +28688,10 @@
         <v>0.002084</v>
       </c>
       <c r="Y246" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z246" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA246" s="3" t="n">
         <v>2</v>
@@ -28788,7 +28788,7 @@
         <v>0.001352</v>
       </c>
       <c r="Y247" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z247" s="3" t="n">
         <v>-0</v>
@@ -28891,7 +28891,7 @@
         <v>0</v>
       </c>
       <c r="Z248" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA248" s="3" t="n">
         <v>0</v>
@@ -28991,7 +28991,7 @@
         <v>-0</v>
       </c>
       <c r="Z249" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA249" s="3" t="n">
         <v>0</v>
@@ -29088,10 +29088,10 @@
         <v>0.001877</v>
       </c>
       <c r="Y250" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z250" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA250" s="3" t="n">
         <v>0</v>
@@ -29188,10 +29188,10 @@
         <v>0.001237</v>
       </c>
       <c r="Y251" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z251" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA251" s="3" t="n">
         <v>5</v>
@@ -29388,10 +29388,10 @@
         <v>0.001506</v>
       </c>
       <c r="Y253" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z253" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA253" s="3" t="n">
         <v>2</v>
@@ -29491,7 +29491,7 @@
         <v>-0</v>
       </c>
       <c r="Z254" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA254" s="3" t="n">
         <v>1</v>
@@ -29688,10 +29688,10 @@
         <v>0.000995</v>
       </c>
       <c r="Y256" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z256" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA256" s="3" t="n">
         <v>0</v>
@@ -29988,7 +29988,7 @@
         <v>0.00134</v>
       </c>
       <c r="Y259" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z259" s="3" t="n">
         <v>0</v>
@@ -30091,7 +30091,7 @@
         <v>-0</v>
       </c>
       <c r="Z260" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA260" s="3" t="n">
         <v>0</v>
@@ -30188,10 +30188,10 @@
         <v>0.001556</v>
       </c>
       <c r="Y261" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z261" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA261" s="3" t="n">
         <v>0</v>
@@ -30291,7 +30291,7 @@
         <v>0</v>
       </c>
       <c r="Z262" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA262" s="3" t="n">
         <v>0</v>
@@ -30588,7 +30588,7 @@
         <v>0.00079</v>
       </c>
       <c r="Y265" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z265" s="3" t="n">
         <v>-0</v>
@@ -30791,7 +30791,7 @@
         <v>-0</v>
       </c>
       <c r="Z267" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA267" s="3" t="n">
         <v>0</v>
@@ -31391,7 +31391,7 @@
         <v>0</v>
       </c>
       <c r="Z273" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA273" s="3" t="n">
         <v>1</v>
@@ -31591,7 +31591,7 @@
         <v>0</v>
       </c>
       <c r="Z275" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA275" s="3" t="n">
         <v>1</v>
@@ -31891,7 +31891,7 @@
         <v>0</v>
       </c>
       <c r="Z278" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA278" s="3" t="n">
         <v>0</v>
@@ -31991,7 +31991,7 @@
         <v>-0</v>
       </c>
       <c r="Z279" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA279" s="3" t="n">
         <v>0</v>
@@ -32188,7 +32188,7 @@
         <v>0.001133</v>
       </c>
       <c r="Y281" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z281" s="3" t="n">
         <v>-0</v>
@@ -32288,10 +32288,10 @@
         <v>0.0009479999999999999</v>
       </c>
       <c r="Y282" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z282" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA282" s="3" t="n">
         <v>0</v>
@@ -32588,7 +32588,7 @@
         <v>0.00143</v>
       </c>
       <c r="Y285" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z285" s="3" t="n">
         <v>0</v>
@@ -32688,10 +32688,10 @@
         <v>0.00209</v>
       </c>
       <c r="Y286" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z286" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA286" s="3" t="n">
         <v>1</v>
@@ -32891,7 +32891,7 @@
         <v>0</v>
       </c>
       <c r="Z288" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA288" s="3" t="n">
         <v>1</v>
@@ -33088,10 +33088,10 @@
         <v>0.00315</v>
       </c>
       <c r="Y290" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z290" s="3" t="n">
         <v>-0</v>
-      </c>
-      <c r="Z290" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="AA290" s="3" t="n">
         <v>0</v>
@@ -33591,7 +33591,7 @@
         <v>-0</v>
       </c>
       <c r="Z295" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA295" s="3" t="n">
         <v>2</v>
@@ -34088,7 +34088,7 @@
         <v>0.001087</v>
       </c>
       <c r="Y300" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z300" s="3" t="n">
         <v>-0</v>
@@ -34288,7 +34288,7 @@
         <v>0.00126</v>
       </c>
       <c r="Y302" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z302" s="3" t="n">
         <v>-0</v>
@@ -34488,10 +34488,10 @@
         <v>0.000908</v>
       </c>
       <c r="Y304" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z304" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA304" s="3" t="n">
         <v>0</v>
@@ -34688,7 +34688,7 @@
         <v>0.001202</v>
       </c>
       <c r="Y306" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z306" s="3" t="n">
         <v>0</v>
@@ -34888,7 +34888,7 @@
         <v>0.001097</v>
       </c>
       <c r="Y308" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z308" s="3" t="n">
         <v>0</v>
@@ -35188,7 +35188,7 @@
         <v>0.001123</v>
       </c>
       <c r="Y311" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z311" s="3" t="n">
         <v>0</v>
@@ -35388,10 +35388,10 @@
         <v>0.001773</v>
       </c>
       <c r="Y313" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z313" s="3" t="n">
         <v>-0</v>
-      </c>
-      <c r="Z313" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="AA313" s="3" t="n">
         <v>1</v>
@@ -35791,7 +35791,7 @@
         <v>0</v>
       </c>
       <c r="Z317" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA317" s="3" t="n">
         <v>0</v>
@@ -36088,10 +36088,10 @@
         <v>0.000803</v>
       </c>
       <c r="Y320" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z320" s="3" t="n">
         <v>-0</v>
-      </c>
-      <c r="Z320" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="AA320" s="3" t="n">
         <v>1</v>
@@ -36488,10 +36488,10 @@
         <v>0.00087</v>
       </c>
       <c r="Y324" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z324" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA324" s="3" t="n">
         <v>0</v>
@@ -37091,7 +37091,7 @@
         <v>0</v>
       </c>
       <c r="Z330" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA330" s="3" t="n">
         <v>0</v>
@@ -37691,7 +37691,7 @@
         <v>0</v>
       </c>
       <c r="Z336" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA336" s="3" t="n">
         <v>1</v>
@@ -37888,10 +37888,10 @@
         <v>0.00122</v>
       </c>
       <c r="Y338" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z338" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA338" s="3" t="n">
         <v>0</v>
@@ -37988,7 +37988,7 @@
         <v>0.001203</v>
       </c>
       <c r="Y339" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z339" s="3" t="n">
         <v>0</v>
@@ -38191,7 +38191,7 @@
         <v>0</v>
       </c>
       <c r="Z341" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA341" s="3" t="n">
         <v>0</v>
@@ -38488,7 +38488,7 @@
         <v>0.000561</v>
       </c>
       <c r="Y344" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z344" s="3" t="n">
         <v>0</v>
@@ -38588,10 +38588,10 @@
         <v>0.000592</v>
       </c>
       <c r="Y345" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z345" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA345" s="3" t="n">
         <v>0</v>
@@ -39388,10 +39388,10 @@
         <v>0.000518</v>
       </c>
       <c r="Y353" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z353" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA353" s="3" t="n">
         <v>0</v>
@@ -39556,10 +39556,10 @@
         <v>0.529801</v>
       </c>
       <c r="Y356" s="3" t="n">
-        <v>0.047472</v>
+        <v>0.172952</v>
       </c>
       <c r="Z356" s="3" t="n">
-        <v>0.078362</v>
+        <v>0.148901</v>
       </c>
       <c r="AB356" s="3" t="n">
         <v>0.599035</v>
@@ -39610,10 +39610,10 @@
         <v>0.445424</v>
       </c>
       <c r="Y358" s="3" t="n">
-        <v>0.380211</v>
+        <v>0.393498</v>
       </c>
       <c r="Z358" s="3" t="n">
-        <v>0.358513</v>
+        <v>0.382398</v>
       </c>
       <c r="AA358" s="3" t="n">
         <v>0.531073</v>
@@ -39985,10 +39985,10 @@
         <v>0.386474</v>
       </c>
       <c r="D8" t="n">
-        <v>0.380211</v>
+        <v>0.393498</v>
       </c>
       <c r="E8" t="n">
-        <v>0.28599</v>
+        <v>0.302585</v>
       </c>
       <c r="F8" t="n">
         <v>0.2988505747126437</v>
@@ -40015,10 +40015,10 @@
         <v>0.216528</v>
       </c>
       <c r="D9" t="n">
-        <v>0.047472</v>
+        <v>0.172952</v>
       </c>
       <c r="E9" t="n">
-        <v>0.034619</v>
+        <v>0.130073</v>
       </c>
       <c r="F9" t="n">
         <v>0.1641791044776119</v>
@@ -40045,10 +40045,10 @@
         <v>0.41859</v>
       </c>
       <c r="D10" t="n">
-        <v>0.323194</v>
+        <v>0.366272</v>
       </c>
       <c r="E10" t="n">
-        <v>0.261212</v>
+        <v>0.297168</v>
       </c>
       <c r="F10" t="n">
         <v>0.3636363636363636</v>
@@ -40075,10 +40075,10 @@
         <v>0.397421</v>
       </c>
       <c r="D11" t="n">
-        <v>0.358513</v>
+        <v>0.382398</v>
       </c>
       <c r="E11" t="n">
-        <v>0.265283</v>
+        <v>0.286491</v>
       </c>
       <c r="F11" t="n">
         <v>0.3333333333333333</v>
@@ -40105,10 +40105,10 @@
         <v>0.219019</v>
       </c>
       <c r="D12" t="n">
-        <v>0.078362</v>
+        <v>0.148901</v>
       </c>
       <c r="E12" t="n">
-        <v>0.05898</v>
+        <v>0.108838</v>
       </c>
       <c r="F12" t="n">
         <v>0.1716417910447761</v>
@@ -40135,10 +40135,10 @@
         <v>0.43754</v>
       </c>
       <c r="D13" t="n">
-        <v>0.310017</v>
+        <v>0.365738</v>
       </c>
       <c r="E13" t="n">
-        <v>0.249899</v>
+        <v>0.296888</v>
       </c>
       <c r="F13" t="n">
         <v>0.3939393939393939</v>

--- a/EpiRank_原/ERA_result_d_0.95_daytime_0.5_loops_309.xlsx
+++ b/EpiRank_原/ERA_result_d_0.95_daytime_0.5_loops_309.xlsx
@@ -714,10 +714,10 @@
         <v>0.012854</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA2" s="3" t="n">
         <v>9</v>
@@ -1179,10 +1179,10 @@
         <v>0.006663</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA5" s="3" t="n">
         <v>11</v>
@@ -1334,10 +1334,10 @@
         <v>0.011776</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA6" s="3" t="n">
         <v>11</v>
@@ -1636,10 +1636,10 @@
         <v>0.016986</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA8" s="3" t="n">
         <v>8</v>
@@ -1938,10 +1938,10 @@
         <v>0.01153</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA10" s="3" t="n">
         <v>4</v>
@@ -2093,10 +2093,10 @@
         <v>0.00946</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA11" s="3" t="n">
         <v>2</v>
@@ -3158,10 +3158,10 @@
         <v>0.008602</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA18" s="3" t="n">
         <v>3</v>
@@ -3308,10 +3308,10 @@
         <v>0.011055</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA19" s="3" t="n">
         <v>8</v>
@@ -4398,10 +4398,10 @@
         <v>0.007025</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA27" s="3" t="n">
         <v>8</v>
@@ -4528,10 +4528,10 @@
         <v>0.010381</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA28" s="3" t="n">
         <v>0</v>
@@ -4918,10 +4918,10 @@
         <v>0.004719</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA31" s="3" t="n">
         <v>7</v>
@@ -5278,10 +5278,10 @@
         <v>0.005248</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA34" s="3" t="n">
         <v>7</v>
@@ -6958,10 +6958,10 @@
         <v>0.004857</v>
       </c>
       <c r="Y48" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z48" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA48" s="3" t="n">
         <v>2</v>
@@ -7201,7 +7201,7 @@
         <v>0</v>
       </c>
       <c r="Z50" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA50" s="3" t="n">
         <v>1</v>
@@ -7318,10 +7318,10 @@
         <v>0.006162</v>
       </c>
       <c r="Y51" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z51" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA51" s="3" t="n">
         <v>5</v>
@@ -7438,10 +7438,10 @@
         <v>0.005847</v>
       </c>
       <c r="Y52" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z52" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA52" s="3" t="n">
         <v>0</v>
@@ -7678,10 +7678,10 @@
         <v>0.005539</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA54" s="3" t="n">
         <v>2</v>
@@ -8398,10 +8398,10 @@
         <v>0.00463</v>
       </c>
       <c r="Y60" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z60" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA60" s="3" t="n">
         <v>6</v>
@@ -8758,10 +8758,10 @@
         <v>0.006417</v>
       </c>
       <c r="Y63" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z63" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA63" s="3" t="n">
         <v>4</v>
@@ -9478,7 +9478,7 @@
         <v>0.003257</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z69" s="3" t="n">
         <v>-0</v>
@@ -10158,10 +10158,10 @@
         <v>0.002652</v>
       </c>
       <c r="Y75" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z75" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA75" s="3" t="n">
         <v>4</v>
@@ -10488,10 +10488,10 @@
         <v>0.004</v>
       </c>
       <c r="Y78" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z78" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA78" s="3" t="n">
         <v>1</v>
@@ -10818,10 +10818,10 @@
         <v>0.004367</v>
       </c>
       <c r="Y81" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z81" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA81" s="3" t="n">
         <v>0</v>
@@ -11038,10 +11038,10 @@
         <v>0.002556</v>
       </c>
       <c r="Y83" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z83" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA83" s="3" t="n">
         <v>2</v>
@@ -11478,10 +11478,10 @@
         <v>0.00305</v>
       </c>
       <c r="Y87" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z87" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA87" s="3" t="n">
         <v>1</v>
@@ -12138,7 +12138,7 @@
         <v>0.003417</v>
       </c>
       <c r="Y93" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z93" s="3" t="n">
         <v>0</v>
@@ -12248,10 +12248,10 @@
         <v>0.002955</v>
       </c>
       <c r="Y94" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z94" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA94" s="3" t="n">
         <v>3</v>
@@ -12358,10 +12358,10 @@
         <v>0.003698</v>
       </c>
       <c r="Y95" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z95" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA95" s="3" t="n">
         <v>0</v>
@@ -12468,10 +12468,10 @@
         <v>0.002274</v>
       </c>
       <c r="Y96" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z96" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA96" s="3" t="n">
         <v>0</v>
@@ -12578,10 +12578,10 @@
         <v>0.003791</v>
       </c>
       <c r="Y97" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z97" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA97" s="3" t="n">
         <v>0</v>
@@ -12908,10 +12908,10 @@
         <v>0.003887</v>
       </c>
       <c r="Y100" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z100" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA100" s="3" t="n">
         <v>0</v>
@@ -13018,10 +13018,10 @@
         <v>0.003378</v>
       </c>
       <c r="Y101" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z101" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA101" s="3" t="n">
         <v>2</v>
@@ -14008,10 +14008,10 @@
         <v>0.00281</v>
       </c>
       <c r="Y110" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z110" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA110" s="3" t="n">
         <v>0</v>
@@ -14448,7 +14448,7 @@
         <v>0.002814</v>
       </c>
       <c r="Y114" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z114" s="3" t="n">
         <v>-0</v>
@@ -15221,7 +15221,7 @@
         <v>0</v>
       </c>
       <c r="Z121" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA121" s="3" t="n">
         <v>2</v>
@@ -15551,7 +15551,7 @@
         <v>0</v>
       </c>
       <c r="Z124" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA124" s="3" t="n">
         <v>0</v>
@@ -15658,10 +15658,10 @@
         <v>0.002464</v>
       </c>
       <c r="Y125" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z125" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA125" s="3" t="n">
         <v>1</v>
@@ -15768,10 +15768,10 @@
         <v>0.002795</v>
       </c>
       <c r="Y126" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z126" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA126" s="3" t="n">
         <v>2</v>
@@ -16098,7 +16098,7 @@
         <v>0.00129</v>
       </c>
       <c r="Y129" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z129" s="3" t="n">
         <v>-0</v>
@@ -16318,10 +16318,10 @@
         <v>0.002388</v>
       </c>
       <c r="Y131" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z131" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA131" s="3" t="n">
         <v>2</v>
@@ -16428,10 +16428,10 @@
         <v>0.001915</v>
       </c>
       <c r="Y132" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z132" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA132" s="3" t="n">
         <v>1</v>
@@ -16541,7 +16541,7 @@
         <v>-0</v>
       </c>
       <c r="Z133" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA133" s="3" t="n">
         <v>1</v>
@@ -16758,10 +16758,10 @@
         <v>0.003318</v>
       </c>
       <c r="Y135" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z135" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA135" s="3" t="n">
         <v>3</v>
@@ -16978,7 +16978,7 @@
         <v>0.002498</v>
       </c>
       <c r="Y137" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z137" s="3" t="n">
         <v>-0</v>
@@ -17088,10 +17088,10 @@
         <v>0.004527</v>
       </c>
       <c r="Y138" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z138" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA138" s="3" t="n">
         <v>0</v>
@@ -17308,10 +17308,10 @@
         <v>0.002586</v>
       </c>
       <c r="Y140" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z140" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA140" s="3" t="n">
         <v>0</v>
@@ -17528,7 +17528,7 @@
         <v>0.001764</v>
       </c>
       <c r="Y142" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z142" s="3" t="n">
         <v>0</v>
@@ -17748,7 +17748,7 @@
         <v>0.001956</v>
       </c>
       <c r="Y144" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z144" s="3" t="n">
         <v>0</v>
@@ -17861,7 +17861,7 @@
         <v>-0</v>
       </c>
       <c r="Z145" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA145" s="3" t="n">
         <v>2</v>
@@ -18738,7 +18738,7 @@
         <v>0.001669</v>
       </c>
       <c r="Y153" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z153" s="3" t="n">
         <v>0</v>
@@ -18851,7 +18851,7 @@
         <v>-0</v>
       </c>
       <c r="Z154" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA154" s="3" t="n">
         <v>0</v>
@@ -19288,10 +19288,10 @@
         <v>0.003412</v>
       </c>
       <c r="Y158" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z158" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA158" s="3" t="n">
         <v>0</v>
@@ -19618,10 +19618,10 @@
         <v>0.004481</v>
       </c>
       <c r="Y161" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z161" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA161" s="3" t="n">
         <v>1</v>
@@ -19948,10 +19948,10 @@
         <v>0.002821</v>
       </c>
       <c r="Y164" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z164" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA164" s="3" t="n">
         <v>1</v>
@@ -20168,10 +20168,10 @@
         <v>0.002439</v>
       </c>
       <c r="Y166" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z166" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA166" s="3" t="n">
         <v>1</v>
@@ -20388,10 +20388,10 @@
         <v>0.001505</v>
       </c>
       <c r="Y168" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z168" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA168" s="3" t="n">
         <v>1</v>
@@ -20498,10 +20498,10 @@
         <v>0.001403</v>
       </c>
       <c r="Y169" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z169" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA169" s="3" t="n">
         <v>1</v>
@@ -20721,7 +20721,7 @@
         <v>0</v>
       </c>
       <c r="Z171" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA171" s="3" t="n">
         <v>1</v>
@@ -20831,7 +20831,7 @@
         <v>0</v>
       </c>
       <c r="Z172" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA172" s="3" t="n">
         <v>0</v>
@@ -20938,10 +20938,10 @@
         <v>0.001802</v>
       </c>
       <c r="Y173" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z173" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA173" s="3" t="n">
         <v>0</v>
@@ -21051,7 +21051,7 @@
         <v>0</v>
       </c>
       <c r="Z174" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA174" s="3" t="n">
         <v>1</v>
@@ -21158,7 +21158,7 @@
         <v>0.003346</v>
       </c>
       <c r="Y175" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z175" s="3" t="n">
         <v>0</v>
@@ -21378,10 +21378,10 @@
         <v>0.001266</v>
       </c>
       <c r="Y177" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z177" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA177" s="3" t="n">
         <v>2</v>
@@ -21708,10 +21708,10 @@
         <v>0.002092</v>
       </c>
       <c r="Y180" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z180" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA180" s="3" t="n">
         <v>0</v>
@@ -21818,10 +21818,10 @@
         <v>0.002941</v>
       </c>
       <c r="Y181" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z181" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA181" s="3" t="n">
         <v>3</v>
@@ -21928,7 +21928,7 @@
         <v>0.001103</v>
       </c>
       <c r="Y182" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z182" s="3" t="n">
         <v>-0</v>
@@ -22038,10 +22038,10 @@
         <v>0.001311</v>
       </c>
       <c r="Y183" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z183" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA183" s="3" t="n">
         <v>0</v>
@@ -22151,7 +22151,7 @@
         <v>-0</v>
       </c>
       <c r="Z184" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA184" s="3" t="n">
         <v>0</v>
@@ -22258,10 +22258,10 @@
         <v>0.00301</v>
       </c>
       <c r="Y185" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z185" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA185" s="3" t="n">
         <v>0</v>
@@ -22478,7 +22478,7 @@
         <v>0.001674</v>
       </c>
       <c r="Y187" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z187" s="3" t="n">
         <v>-0</v>
@@ -22588,10 +22588,10 @@
         <v>0.00262</v>
       </c>
       <c r="Y188" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z188" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA188" s="3" t="n">
         <v>0</v>
@@ -22808,10 +22808,10 @@
         <v>0.003025</v>
       </c>
       <c r="Y190" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z190" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA190" s="3" t="n">
         <v>5</v>
@@ -22918,10 +22918,10 @@
         <v>0.002244</v>
       </c>
       <c r="Y191" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z191" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA191" s="3" t="n">
         <v>0</v>
@@ -23138,7 +23138,7 @@
         <v>0.001708</v>
       </c>
       <c r="Y193" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z193" s="3" t="n">
         <v>0</v>
@@ -23251,7 +23251,7 @@
         <v>0</v>
       </c>
       <c r="Z194" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA194" s="3" t="n">
         <v>1</v>
@@ -23471,7 +23471,7 @@
         <v>0</v>
       </c>
       <c r="Z196" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA196" s="3" t="n">
         <v>1</v>
@@ -23578,7 +23578,7 @@
         <v>0.001196</v>
       </c>
       <c r="Y197" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z197" s="3" t="n">
         <v>-0</v>
@@ -23688,10 +23688,10 @@
         <v>0.001855</v>
       </c>
       <c r="Y198" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z198" s="3" t="n">
         <v>-0</v>
-      </c>
-      <c r="Z198" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="AA198" s="3" t="n">
         <v>2</v>
@@ -23801,7 +23801,7 @@
         <v>0</v>
       </c>
       <c r="Z199" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA199" s="3" t="n">
         <v>1</v>
@@ -23908,7 +23908,7 @@
         <v>0.001262</v>
       </c>
       <c r="Y200" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z200" s="3" t="n">
         <v>0</v>
@@ -24238,7 +24238,7 @@
         <v>0.001311</v>
       </c>
       <c r="Y203" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z203" s="3" t="n">
         <v>-0</v>
@@ -24458,10 +24458,10 @@
         <v>0.001787</v>
       </c>
       <c r="Y205" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z205" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA205" s="3" t="n">
         <v>2</v>
@@ -25118,10 +25118,10 @@
         <v>0.001083</v>
       </c>
       <c r="Y211" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z211" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA211" s="3" t="n">
         <v>3</v>
@@ -25448,10 +25448,10 @@
         <v>0.002065</v>
       </c>
       <c r="Y214" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z214" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA214" s="3" t="n">
         <v>0</v>
@@ -25558,10 +25558,10 @@
         <v>0.0008140000000000001</v>
       </c>
       <c r="Y215" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z215" s="3" t="n">
         <v>-0</v>
-      </c>
-      <c r="Z215" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="AA215" s="3" t="n">
         <v>0</v>
@@ -25668,7 +25668,7 @@
         <v>0.000907</v>
       </c>
       <c r="Y216" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z216" s="3" t="n">
         <v>-0</v>
@@ -25978,7 +25978,7 @@
         <v>0.001444</v>
       </c>
       <c r="Y219" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z219" s="3" t="n">
         <v>-0</v>
@@ -26078,10 +26078,10 @@
         <v>0.001942</v>
       </c>
       <c r="Y220" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z220" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA220" s="3" t="n">
         <v>0</v>
@@ -26281,7 +26281,7 @@
         <v>0</v>
       </c>
       <c r="Z222" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA222" s="3" t="n">
         <v>6</v>
@@ -26478,7 +26478,7 @@
         <v>0.001353</v>
       </c>
       <c r="Y224" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z224" s="3" t="n">
         <v>0</v>
@@ -26678,7 +26678,7 @@
         <v>0.001152</v>
       </c>
       <c r="Y226" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z226" s="3" t="n">
         <v>-0</v>
@@ -26878,7 +26878,7 @@
         <v>0.001253</v>
       </c>
       <c r="Y228" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z228" s="3" t="n">
         <v>0</v>
@@ -26981,7 +26981,7 @@
         <v>0</v>
       </c>
       <c r="Z229" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA229" s="3" t="n">
         <v>2</v>
@@ -27178,10 +27178,10 @@
         <v>0.001512</v>
       </c>
       <c r="Y231" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z231" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA231" s="3" t="n">
         <v>0</v>
@@ -27578,10 +27578,10 @@
         <v>0.000998</v>
       </c>
       <c r="Y235" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z235" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA235" s="3" t="n">
         <v>1</v>
@@ -27678,7 +27678,7 @@
         <v>0.001639</v>
       </c>
       <c r="Y236" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z236" s="3" t="n">
         <v>-0</v>
@@ -27778,7 +27778,7 @@
         <v>0.001039</v>
       </c>
       <c r="Y237" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z237" s="3" t="n">
         <v>-0</v>
@@ -27881,7 +27881,7 @@
         <v>0</v>
       </c>
       <c r="Z238" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA238" s="3" t="n">
         <v>2</v>
@@ -28278,10 +28278,10 @@
         <v>0.001251</v>
       </c>
       <c r="Y242" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z242" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA242" s="3" t="n">
         <v>0</v>
@@ -28578,7 +28578,7 @@
         <v>0.001356</v>
       </c>
       <c r="Y245" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z245" s="3" t="n">
         <v>-0</v>
@@ -28678,10 +28678,10 @@
         <v>0.002083</v>
       </c>
       <c r="Y246" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z246" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA246" s="3" t="n">
         <v>2</v>
@@ -28778,10 +28778,10 @@
         <v>0.002004</v>
       </c>
       <c r="Y247" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z247" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA247" s="3" t="n">
         <v>0</v>
@@ -28881,7 +28881,7 @@
         <v>-0</v>
       </c>
       <c r="Z248" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA248" s="3" t="n">
         <v>0</v>
@@ -29378,7 +29378,7 @@
         <v>0.0013</v>
       </c>
       <c r="Y253" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z253" s="3" t="n">
         <v>-0</v>
@@ -29681,7 +29681,7 @@
         <v>-0</v>
       </c>
       <c r="Z256" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA256" s="3" t="n">
         <v>2</v>
@@ -29778,7 +29778,7 @@
         <v>0.001343</v>
       </c>
       <c r="Y257" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z257" s="3" t="n">
         <v>0</v>
@@ -29878,7 +29878,7 @@
         <v>0.000868</v>
       </c>
       <c r="Y258" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z258" s="3" t="n">
         <v>0</v>
@@ -29978,7 +29978,7 @@
         <v>0.0009890000000000001</v>
       </c>
       <c r="Y259" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z259" s="3" t="n">
         <v>0</v>
@@ -30278,7 +30278,7 @@
         <v>0.001549</v>
       </c>
       <c r="Y262" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z262" s="3" t="n">
         <v>0</v>
@@ -30378,10 +30378,10 @@
         <v>0.000786</v>
       </c>
       <c r="Y263" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z263" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA263" s="3" t="n">
         <v>0</v>
@@ -30681,7 +30681,7 @@
         <v>-0</v>
       </c>
       <c r="Z266" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA266" s="3" t="n">
         <v>0</v>
@@ -30778,7 +30778,7 @@
         <v>0.001385</v>
       </c>
       <c r="Y267" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z267" s="3" t="n">
         <v>0</v>
@@ -31178,10 +31178,10 @@
         <v>0.000784</v>
       </c>
       <c r="Y271" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z271" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA271" s="3" t="n">
         <v>1</v>
@@ -31378,10 +31378,10 @@
         <v>0.000806</v>
       </c>
       <c r="Y273" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z273" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA273" s="3" t="n">
         <v>1</v>
@@ -31578,7 +31578,7 @@
         <v>0.001022</v>
       </c>
       <c r="Y275" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z275" s="3" t="n">
         <v>0</v>
@@ -31778,10 +31778,10 @@
         <v>0.001035</v>
       </c>
       <c r="Y277" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z277" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA277" s="3" t="n">
         <v>0</v>
@@ -31878,10 +31878,10 @@
         <v>0.000885</v>
       </c>
       <c r="Y278" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z278" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA278" s="3" t="n">
         <v>0</v>
@@ -32081,7 +32081,7 @@
         <v>-0</v>
       </c>
       <c r="Z280" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA280" s="3" t="n">
         <v>0</v>
@@ -32278,10 +32278,10 @@
         <v>0.00095</v>
       </c>
       <c r="Y282" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z282" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA282" s="3" t="n">
         <v>0</v>
@@ -32578,7 +32578,7 @@
         <v>0.002094</v>
       </c>
       <c r="Y285" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z285" s="3" t="n">
         <v>0</v>
@@ -32678,10 +32678,10 @@
         <v>0.000873</v>
       </c>
       <c r="Y286" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z286" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA286" s="3" t="n">
         <v>1</v>
@@ -32878,7 +32878,7 @@
         <v>0.001409</v>
       </c>
       <c r="Y288" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z288" s="3" t="n">
         <v>-0</v>
@@ -32978,10 +32978,10 @@
         <v>0.003156</v>
       </c>
       <c r="Y289" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z289" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA289" s="3" t="n">
         <v>0</v>
@@ -33078,10 +33078,10 @@
         <v>0.001083</v>
       </c>
       <c r="Y290" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z290" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA290" s="3" t="n">
         <v>2</v>
@@ -33178,10 +33178,10 @@
         <v>0.001187</v>
       </c>
       <c r="Y291" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z291" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA291" s="3" t="n">
         <v>0</v>
@@ -33578,7 +33578,7 @@
         <v>0.00138</v>
       </c>
       <c r="Y295" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z295" s="3" t="n">
         <v>0</v>
@@ -33681,7 +33681,7 @@
         <v>0</v>
       </c>
       <c r="Z296" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA296" s="3" t="n">
         <v>1</v>
@@ -33978,10 +33978,10 @@
         <v>0.00109</v>
       </c>
       <c r="Y299" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z299" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA299" s="3" t="n">
         <v>9</v>
@@ -34178,7 +34178,7 @@
         <v>0.001263</v>
       </c>
       <c r="Y301" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z301" s="3" t="n">
         <v>0</v>
@@ -34578,7 +34578,7 @@
         <v>0.001206</v>
       </c>
       <c r="Y305" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z305" s="3" t="n">
         <v>-0</v>
@@ -34678,10 +34678,10 @@
         <v>0.000829</v>
       </c>
       <c r="Y306" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z306" s="3" t="n">
         <v>-0</v>
-      </c>
-      <c r="Z306" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="AA306" s="3" t="n">
         <v>0</v>
@@ -34778,10 +34778,10 @@
         <v>0.0011</v>
       </c>
       <c r="Y307" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z307" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA307" s="3" t="n">
         <v>0</v>
@@ -34878,7 +34878,7 @@
         <v>0.000804</v>
       </c>
       <c r="Y308" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z308" s="3" t="n">
         <v>0</v>
@@ -35078,10 +35078,10 @@
         <v>0.001126</v>
       </c>
       <c r="Y310" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z310" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA310" s="3" t="n">
         <v>0</v>
@@ -35378,7 +35378,7 @@
         <v>0.000775</v>
       </c>
       <c r="Y313" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z313" s="3" t="n">
         <v>0</v>
@@ -35678,10 +35678,10 @@
         <v>0.000922</v>
       </c>
       <c r="Y316" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z316" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA316" s="3" t="n">
         <v>0</v>
@@ -35881,7 +35881,7 @@
         <v>-0</v>
       </c>
       <c r="Z318" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA318" s="3" t="n">
         <v>3</v>
@@ -36081,7 +36081,7 @@
         <v>0</v>
       </c>
       <c r="Z320" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA320" s="3" t="n">
         <v>1</v>
@@ -36178,10 +36178,10 @@
         <v>0.000802</v>
       </c>
       <c r="Y321" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z321" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA321" s="3" t="n">
         <v>1</v>
@@ -36378,7 +36378,7 @@
         <v>0.0008720000000000001</v>
       </c>
       <c r="Y323" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z323" s="3" t="n">
         <v>0</v>
@@ -37581,7 +37581,7 @@
         <v>-0</v>
       </c>
       <c r="Z335" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA335" s="3" t="n">
         <v>1</v>
@@ -37778,10 +37778,10 @@
         <v>0.001217</v>
       </c>
       <c r="Y337" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z337" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA337" s="3" t="n">
         <v>0</v>
@@ -37978,10 +37978,10 @@
         <v>0.001199</v>
       </c>
       <c r="Y339" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z339" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA339" s="3" t="n">
         <v>0</v>
@@ -38078,10 +38078,10 @@
         <v>0.001205</v>
       </c>
       <c r="Y340" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z340" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA340" s="3" t="n">
         <v>0</v>
@@ -38378,10 +38378,10 @@
         <v>0.000563</v>
       </c>
       <c r="Y343" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z343" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA343" s="3" t="n">
         <v>0</v>
@@ -38578,10 +38578,10 @@
         <v>0.000592</v>
       </c>
       <c r="Y345" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z345" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA345" s="3" t="n">
         <v>0</v>
@@ -39278,10 +39278,10 @@
         <v>0.000518</v>
       </c>
       <c r="Y352" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z352" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA352" s="3" t="n">
         <v>0</v>
@@ -39446,10 +39446,10 @@
         <v>0.531477</v>
       </c>
       <c r="Y355" s="3" t="n">
-        <v>0.019874</v>
+        <v>0.17994</v>
       </c>
       <c r="Z355" s="3" t="n">
-        <v>0.03652</v>
+        <v>0.177969</v>
       </c>
       <c r="AB355" s="3" t="n">
         <v>0.599397</v>
@@ -39500,10 +39500,10 @@
         <v>0.44762</v>
       </c>
       <c r="Y357" s="3" t="n">
-        <v>0.312399</v>
+        <v>0.399856</v>
       </c>
       <c r="Z357" s="3" t="n">
-        <v>0.294089</v>
+        <v>0.410775</v>
       </c>
       <c r="AA357" s="3" t="n">
         <v>0.534075</v>
@@ -39625,7 +39625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -39636,6 +39636,8 @@
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -39666,15 +39668,25 @@
       </c>
       <c r="F1" s="4" t="inlineStr">
         <is>
+          <t>Pearson_partial_r</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Spearman_partial_rho</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
           <t>Recall</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>Precision</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
@@ -39701,12 +39713,18 @@
         <v>0.396772</v>
       </c>
       <c r="F2" t="n">
+        <v>0.107116</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.06419</v>
+      </c>
+      <c r="H2" t="n">
         <v>0.7272727272727273</v>
       </c>
-      <c r="G2" t="n">
+      <c r="I2" t="n">
         <v>0.5470085470085471</v>
       </c>
-      <c r="H2" t="n">
+      <c r="J2" t="n">
         <v>0.624390243902439</v>
       </c>
     </row>
@@ -39731,12 +39749,18 @@
         <v>0.449826</v>
       </c>
       <c r="F3" t="n">
+        <v>0.229239</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.0648</v>
+      </c>
+      <c r="H3" t="n">
         <v>0.6074074074074074</v>
       </c>
-      <c r="G3" t="n">
+      <c r="I3" t="n">
         <v>0.7008547008547008</v>
       </c>
-      <c r="H3" t="n">
+      <c r="J3" t="n">
         <v>0.6507936507936508</v>
       </c>
     </row>
@@ -39761,12 +39785,18 @@
         <v>0.275768</v>
       </c>
       <c r="F4" t="n">
+        <v>-0.021728</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-0.005949</v>
+      </c>
+      <c r="H4" t="n">
         <v>0.6818181818181818</v>
       </c>
-      <c r="G4" t="n">
+      <c r="I4" t="n">
         <v>0.3846153846153846</v>
       </c>
-      <c r="H4" t="n">
+      <c r="J4" t="n">
         <v>0.4918032786885246</v>
       </c>
     </row>
@@ -39791,12 +39821,18 @@
         <v>0.326574</v>
       </c>
       <c r="F5" t="n">
+        <v>0.062137</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.029295</v>
+      </c>
+      <c r="H5" t="n">
         <v>0.6136363636363636</v>
       </c>
-      <c r="G5" t="n">
+      <c r="I5" t="n">
         <v>0.5142857142857142</v>
       </c>
-      <c r="H5" t="n">
+      <c r="J5" t="n">
         <v>0.5595854922279793</v>
       </c>
     </row>
@@ -39821,12 +39857,18 @@
         <v>0.38949</v>
       </c>
       <c r="F6" t="n">
+        <v>0.191857</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.08333400000000001</v>
+      </c>
+      <c r="H6" t="n">
         <v>0.5185185185185185</v>
       </c>
-      <c r="G6" t="n">
+      <c r="I6" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="H6" t="n">
+      <c r="J6" t="n">
         <v>0.5833333333333334</v>
       </c>
     </row>
@@ -39851,12 +39893,18 @@
         <v>0.214899</v>
       </c>
       <c r="F7" t="n">
+        <v>-0.044173</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-0.039888</v>
+      </c>
+      <c r="H7" t="n">
         <v>0.5606060606060606</v>
       </c>
-      <c r="G7" t="n">
+      <c r="I7" t="n">
         <v>0.3523809523809524</v>
       </c>
-      <c r="H7" t="n">
+      <c r="J7" t="n">
         <v>0.4327485380116959</v>
       </c>
     </row>
@@ -39875,18 +39923,24 @@
         <v>0.386366</v>
       </c>
       <c r="D8" t="n">
-        <v>0.312399</v>
+        <v>0.399856</v>
       </c>
       <c r="E8" t="n">
-        <v>0.243697</v>
+        <v>0.307601</v>
       </c>
       <c r="F8" t="n">
+        <v>0.143097</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.162728</v>
+      </c>
+      <c r="H8" t="n">
         <v>0.2954545454545455</v>
       </c>
-      <c r="G8" t="n">
+      <c r="I8" t="n">
         <v>1</v>
       </c>
-      <c r="H8" t="n">
+      <c r="J8" t="n">
         <v>0.456140350877193</v>
       </c>
     </row>
@@ -39905,18 +39959,24 @@
         <v>0.21634</v>
       </c>
       <c r="D9" t="n">
-        <v>0.019874</v>
+        <v>0.17994</v>
       </c>
       <c r="E9" t="n">
-        <v>0.015698</v>
+        <v>0.135574</v>
       </c>
       <c r="F9" t="n">
+        <v>0.055515</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-0.261489</v>
+      </c>
+      <c r="H9" t="n">
         <v>0.162962962962963</v>
       </c>
-      <c r="G9" t="n">
+      <c r="I9" t="n">
         <v>0.8461538461538461</v>
       </c>
-      <c r="H9" t="n">
+      <c r="J9" t="n">
         <v>0.2732919254658385</v>
       </c>
     </row>
@@ -39935,18 +39995,24 @@
         <v>0.418566</v>
       </c>
       <c r="D10" t="n">
-        <v>0.301465</v>
+        <v>0.38599</v>
       </c>
       <c r="E10" t="n">
-        <v>0.243588</v>
+        <v>0.314132</v>
       </c>
       <c r="F10" t="n">
+        <v>0.345677</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.229682</v>
+      </c>
+      <c r="H10" t="n">
         <v>0.3636363636363636</v>
       </c>
-      <c r="G10" t="n">
+      <c r="I10" t="n">
         <v>0.9230769230769231</v>
       </c>
-      <c r="H10" t="n">
+      <c r="J10" t="n">
         <v>0.5217391304347827</v>
       </c>
     </row>
@@ -39965,18 +40031,24 @@
         <v>0.397306</v>
       </c>
       <c r="D11" t="n">
-        <v>0.294089</v>
+        <v>0.410775</v>
       </c>
       <c r="E11" t="n">
-        <v>0.223126</v>
+        <v>0.315117</v>
       </c>
       <c r="F11" t="n">
+        <v>0.15142</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.191114</v>
+      </c>
+      <c r="H11" t="n">
         <v>0.3295454545454545</v>
       </c>
-      <c r="G11" t="n">
+      <c r="I11" t="n">
         <v>1</v>
       </c>
-      <c r="H11" t="n">
+      <c r="J11" t="n">
         <v>0.4957264957264957</v>
       </c>
     </row>
@@ -39995,18 +40067,24 @@
         <v>0.218819</v>
       </c>
       <c r="D12" t="n">
-        <v>0.03652</v>
+        <v>0.177969</v>
       </c>
       <c r="E12" t="n">
-        <v>0.030566</v>
+        <v>0.131494</v>
       </c>
       <c r="F12" t="n">
+        <v>0.050942</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-0.245763</v>
+      </c>
+      <c r="H12" t="n">
         <v>0.1703703703703704</v>
       </c>
-      <c r="G12" t="n">
+      <c r="I12" t="n">
         <v>0.7931034482758621</v>
       </c>
-      <c r="H12" t="n">
+      <c r="J12" t="n">
         <v>0.2804878048780488</v>
       </c>
     </row>
@@ -40025,18 +40103,24 @@
         <v>0.437514</v>
       </c>
       <c r="D13" t="n">
-        <v>0.306923</v>
+        <v>0.373555</v>
       </c>
       <c r="E13" t="n">
-        <v>0.248819</v>
+        <v>0.303725</v>
       </c>
       <c r="F13" t="n">
+        <v>0.364928</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.220321</v>
+      </c>
+      <c r="H13" t="n">
         <v>0.3939393939393939</v>
       </c>
-      <c r="G13" t="n">
+      <c r="I13" t="n">
         <v>0.896551724137931</v>
       </c>
-      <c r="H13" t="n">
+      <c r="J13" t="n">
         <v>0.5473684210526315</v>
       </c>
     </row>
@@ -40061,12 +40145,18 @@
         <v>0.5249200000000001</v>
       </c>
       <c r="F14" t="n">
+        <v/>
+      </c>
+      <c r="G14" t="n">
+        <v/>
+      </c>
+      <c r="H14" t="n">
         <v>0.7840909090909091</v>
       </c>
-      <c r="G14" t="n">
+      <c r="I14" t="n">
         <v>0.6764705882352942</v>
       </c>
-      <c r="H14" t="n">
+      <c r="J14" t="n">
         <v>0.7263157894736842</v>
       </c>
     </row>
@@ -40091,12 +40181,18 @@
         <v>0.603083</v>
       </c>
       <c r="F15" t="n">
+        <v/>
+      </c>
+      <c r="G15" t="n">
+        <v/>
+      </c>
+      <c r="H15" t="n">
         <v>0.6148148148148148</v>
       </c>
-      <c r="G15" t="n">
+      <c r="I15" t="n">
         <v>0.8137254901960784</v>
       </c>
-      <c r="H15" t="n">
+      <c r="J15" t="n">
         <v>0.70042194092827</v>
       </c>
     </row>
@@ -40121,12 +40217,18 @@
         <v>0.382877</v>
       </c>
       <c r="F16" t="n">
+        <v/>
+      </c>
+      <c r="G16" t="n">
+        <v/>
+      </c>
+      <c r="H16" t="n">
         <v>0.696969696969697</v>
       </c>
-      <c r="G16" t="n">
+      <c r="I16" t="n">
         <v>0.4509803921568628</v>
       </c>
-      <c r="H16" t="n">
+      <c r="J16" t="n">
         <v>0.5476190476190477</v>
       </c>
     </row>
